--- a/templates/xlsx/offer-scorecard.xlsx
+++ b/templates/xlsx/offer-scorecard.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T203"/>
+  <dimension ref="A1:W203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.71428571428572" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,9 @@
     <col width="15.71428571428571" customWidth="1" min="18" max="18"/>
     <col width="15.71428571428571" customWidth="1" min="19" max="19"/>
     <col width="15.71428571428571" customWidth="1" min="20" max="20"/>
+    <col width="15.71428571428571" customWidth="1" min="21" max="21"/>
+    <col width="15.71428571428571" customWidth="1" min="22" max="22"/>
+    <col width="15.71428571428571" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -558,25 +561,40 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Cash tied up across batches in motion (stock + in transit + in production)</t>
+          <t>Batch 1: stock in destination warehouse ($)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Batch 2: stock in transit ($)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Batch 3: stock in production ($)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Cash locked across the three batches ƒ</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Max cash you can afford to lock up</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Cash exposure ƒ</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Independent signals (need ≥3)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
@@ -642,19 +660,29 @@
         <v/>
       </c>
       <c r="P2" s="4" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="Q2" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="S2" s="5">
+        <f>IF(A2="","",P2+Q2+R2)</f>
+        <v/>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="R2" s="3">
-        <f>IF(A2="","",IF(Q2=0,"Set a cap",IF(P2&gt;Q2,"Over cap - shrink batch","OK")))</f>
-        <v/>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" s="3">
+        <f>IF(A2="","",IF(T2=0,"Set a cap",IF(S2&gt;T2,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
+        <v/>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
@@ -686,8 +714,14 @@
       </c>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="3">
-        <f>IF(A3="","",IF(Q3=0,"Set a cap",IF(P3&gt;Q3,"Over cap - shrink batch","OK")))</f>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="5">
+        <f>IF(A3="","",P3+Q3+R3)</f>
+        <v/>
+      </c>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="3">
+        <f>IF(A3="","",IF(T3=0,"Set a cap",IF(S3&gt;T3,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -717,8 +751,14 @@
       </c>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="3">
-        <f>IF(A4="","",IF(Q4=0,"Set a cap",IF(P4&gt;Q4,"Over cap - shrink batch","OK")))</f>
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="5">
+        <f>IF(A4="","",P4+Q4+R4)</f>
+        <v/>
+      </c>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="3">
+        <f>IF(A4="","",IF(T4=0,"Set a cap",IF(S4&gt;T4,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -748,8 +788,14 @@
       </c>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="3">
-        <f>IF(A5="","",IF(Q5=0,"Set a cap",IF(P5&gt;Q5,"Over cap - shrink batch","OK")))</f>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="5">
+        <f>IF(A5="","",P5+Q5+R5)</f>
+        <v/>
+      </c>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="3">
+        <f>IF(A5="","",IF(T5=0,"Set a cap",IF(S5&gt;T5,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -779,8 +825,14 @@
       </c>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="3">
-        <f>IF(A6="","",IF(Q6=0,"Set a cap",IF(P6&gt;Q6,"Over cap - shrink batch","OK")))</f>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="5">
+        <f>IF(A6="","",P6+Q6+R6)</f>
+        <v/>
+      </c>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="3">
+        <f>IF(A6="","",IF(T6=0,"Set a cap",IF(S6&gt;T6,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -810,8 +862,14 @@
       </c>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="3">
-        <f>IF(A7="","",IF(Q7=0,"Set a cap",IF(P7&gt;Q7,"Over cap - shrink batch","OK")))</f>
+      <c r="R7" s="4" t="n"/>
+      <c r="S7" s="5">
+        <f>IF(A7="","",P7+Q7+R7)</f>
+        <v/>
+      </c>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="3">
+        <f>IF(A7="","",IF(T7=0,"Set a cap",IF(S7&gt;T7,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -841,8 +899,14 @@
       </c>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="3">
-        <f>IF(A8="","",IF(Q8=0,"Set a cap",IF(P8&gt;Q8,"Over cap - shrink batch","OK")))</f>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="5">
+        <f>IF(A8="","",P8+Q8+R8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="3">
+        <f>IF(A8="","",IF(T8=0,"Set a cap",IF(S8&gt;T8,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -872,8 +936,14 @@
       </c>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="3">
-        <f>IF(A9="","",IF(Q9=0,"Set a cap",IF(P9&gt;Q9,"Over cap - shrink batch","OK")))</f>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="5">
+        <f>IF(A9="","",P9+Q9+R9)</f>
+        <v/>
+      </c>
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="3">
+        <f>IF(A9="","",IF(T9=0,"Set a cap",IF(S9&gt;T9,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -903,8 +973,14 @@
       </c>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="3">
-        <f>IF(A10="","",IF(Q10=0,"Set a cap",IF(P10&gt;Q10,"Over cap - shrink batch","OK")))</f>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="5">
+        <f>IF(A10="","",P10+Q10+R10)</f>
+        <v/>
+      </c>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="3">
+        <f>IF(A10="","",IF(T10=0,"Set a cap",IF(S10&gt;T10,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -934,8 +1010,14 @@
       </c>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="3">
-        <f>IF(A11="","",IF(Q11=0,"Set a cap",IF(P11&gt;Q11,"Over cap - shrink batch","OK")))</f>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="5">
+        <f>IF(A11="","",P11+Q11+R11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="3">
+        <f>IF(A11="","",IF(T11=0,"Set a cap",IF(S11&gt;T11,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -965,8 +1047,14 @@
       </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="3">
-        <f>IF(A12="","",IF(Q12=0,"Set a cap",IF(P12&gt;Q12,"Over cap - shrink batch","OK")))</f>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="5">
+        <f>IF(A12="","",P12+Q12+R12)</f>
+        <v/>
+      </c>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="3">
+        <f>IF(A12="","",IF(T12=0,"Set a cap",IF(S12&gt;T12,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -996,8 +1084,14 @@
       </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="3">
-        <f>IF(A13="","",IF(Q13=0,"Set a cap",IF(P13&gt;Q13,"Over cap - shrink batch","OK")))</f>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="5">
+        <f>IF(A13="","",P13+Q13+R13)</f>
+        <v/>
+      </c>
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="3">
+        <f>IF(A13="","",IF(T13=0,"Set a cap",IF(S13&gt;T13,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1027,8 +1121,14 @@
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="3">
-        <f>IF(A14="","",IF(Q14=0,"Set a cap",IF(P14&gt;Q14,"Over cap - shrink batch","OK")))</f>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="5">
+        <f>IF(A14="","",P14+Q14+R14)</f>
+        <v/>
+      </c>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="3">
+        <f>IF(A14="","",IF(T14=0,"Set a cap",IF(S14&gt;T14,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1058,8 +1158,14 @@
       </c>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="3">
-        <f>IF(A15="","",IF(Q15=0,"Set a cap",IF(P15&gt;Q15,"Over cap - shrink batch","OK")))</f>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="5">
+        <f>IF(A15="","",P15+Q15+R15)</f>
+        <v/>
+      </c>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="3">
+        <f>IF(A15="","",IF(T15=0,"Set a cap",IF(S15&gt;T15,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1089,8 +1195,14 @@
       </c>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="3">
-        <f>IF(A16="","",IF(Q16=0,"Set a cap",IF(P16&gt;Q16,"Over cap - shrink batch","OK")))</f>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="5">
+        <f>IF(A16="","",P16+Q16+R16)</f>
+        <v/>
+      </c>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="3">
+        <f>IF(A16="","",IF(T16=0,"Set a cap",IF(S16&gt;T16,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1120,8 +1232,14 @@
       </c>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="3">
-        <f>IF(A17="","",IF(Q17=0,"Set a cap",IF(P17&gt;Q17,"Over cap - shrink batch","OK")))</f>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="5">
+        <f>IF(A17="","",P17+Q17+R17)</f>
+        <v/>
+      </c>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="3">
+        <f>IF(A17="","",IF(T17=0,"Set a cap",IF(S17&gt;T17,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1151,8 +1269,14 @@
       </c>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="3">
-        <f>IF(A18="","",IF(Q18=0,"Set a cap",IF(P18&gt;Q18,"Over cap - shrink batch","OK")))</f>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="5">
+        <f>IF(A18="","",P18+Q18+R18)</f>
+        <v/>
+      </c>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="3">
+        <f>IF(A18="","",IF(T18=0,"Set a cap",IF(S18&gt;T18,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1182,8 +1306,14 @@
       </c>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="3">
-        <f>IF(A19="","",IF(Q19=0,"Set a cap",IF(P19&gt;Q19,"Over cap - shrink batch","OK")))</f>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="5">
+        <f>IF(A19="","",P19+Q19+R19)</f>
+        <v/>
+      </c>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="3">
+        <f>IF(A19="","",IF(T19=0,"Set a cap",IF(S19&gt;T19,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1213,8 +1343,14 @@
       </c>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="3">
-        <f>IF(A20="","",IF(Q20=0,"Set a cap",IF(P20&gt;Q20,"Over cap - shrink batch","OK")))</f>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="5">
+        <f>IF(A20="","",P20+Q20+R20)</f>
+        <v/>
+      </c>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="3">
+        <f>IF(A20="","",IF(T20=0,"Set a cap",IF(S20&gt;T20,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1244,8 +1380,14 @@
       </c>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="3">
-        <f>IF(A21="","",IF(Q21=0,"Set a cap",IF(P21&gt;Q21,"Over cap - shrink batch","OK")))</f>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="5">
+        <f>IF(A21="","",P21+Q21+R21)</f>
+        <v/>
+      </c>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="3">
+        <f>IF(A21="","",IF(T21=0,"Set a cap",IF(S21&gt;T21,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1275,8 +1417,14 @@
       </c>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="3">
-        <f>IF(A22="","",IF(Q22=0,"Set a cap",IF(P22&gt;Q22,"Over cap - shrink batch","OK")))</f>
+      <c r="R22" s="4" t="n"/>
+      <c r="S22" s="5">
+        <f>IF(A22="","",P22+Q22+R22)</f>
+        <v/>
+      </c>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="3">
+        <f>IF(A22="","",IF(T22=0,"Set a cap",IF(S22&gt;T22,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1306,8 +1454,14 @@
       </c>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="3">
-        <f>IF(A23="","",IF(Q23=0,"Set a cap",IF(P23&gt;Q23,"Over cap - shrink batch","OK")))</f>
+      <c r="R23" s="4" t="n"/>
+      <c r="S23" s="5">
+        <f>IF(A23="","",P23+Q23+R23)</f>
+        <v/>
+      </c>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="3">
+        <f>IF(A23="","",IF(T23=0,"Set a cap",IF(S23&gt;T23,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1337,8 +1491,14 @@
       </c>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="3">
-        <f>IF(A24="","",IF(Q24=0,"Set a cap",IF(P24&gt;Q24,"Over cap - shrink batch","OK")))</f>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="5">
+        <f>IF(A24="","",P24+Q24+R24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="3">
+        <f>IF(A24="","",IF(T24=0,"Set a cap",IF(S24&gt;T24,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1368,8 +1528,14 @@
       </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="3">
-        <f>IF(A25="","",IF(Q25=0,"Set a cap",IF(P25&gt;Q25,"Over cap - shrink batch","OK")))</f>
+      <c r="R25" s="4" t="n"/>
+      <c r="S25" s="5">
+        <f>IF(A25="","",P25+Q25+R25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="3">
+        <f>IF(A25="","",IF(T25=0,"Set a cap",IF(S25&gt;T25,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1399,8 +1565,14 @@
       </c>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="3">
-        <f>IF(A26="","",IF(Q26=0,"Set a cap",IF(P26&gt;Q26,"Over cap - shrink batch","OK")))</f>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="5">
+        <f>IF(A26="","",P26+Q26+R26)</f>
+        <v/>
+      </c>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="3">
+        <f>IF(A26="","",IF(T26=0,"Set a cap",IF(S26&gt;T26,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1430,8 +1602,14 @@
       </c>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
-      <c r="R27" s="3">
-        <f>IF(A27="","",IF(Q27=0,"Set a cap",IF(P27&gt;Q27,"Over cap - shrink batch","OK")))</f>
+      <c r="R27" s="4" t="n"/>
+      <c r="S27" s="5">
+        <f>IF(A27="","",P27+Q27+R27)</f>
+        <v/>
+      </c>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="3">
+        <f>IF(A27="","",IF(T27=0,"Set a cap",IF(S27&gt;T27,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1461,8 +1639,14 @@
       </c>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="3">
-        <f>IF(A28="","",IF(Q28=0,"Set a cap",IF(P28&gt;Q28,"Over cap - shrink batch","OK")))</f>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="5">
+        <f>IF(A28="","",P28+Q28+R28)</f>
+        <v/>
+      </c>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="3">
+        <f>IF(A28="","",IF(T28=0,"Set a cap",IF(S28&gt;T28,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1492,8 +1676,14 @@
       </c>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
-      <c r="R29" s="3">
-        <f>IF(A29="","",IF(Q29=0,"Set a cap",IF(P29&gt;Q29,"Over cap - shrink batch","OK")))</f>
+      <c r="R29" s="4" t="n"/>
+      <c r="S29" s="5">
+        <f>IF(A29="","",P29+Q29+R29)</f>
+        <v/>
+      </c>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="3">
+        <f>IF(A29="","",IF(T29=0,"Set a cap",IF(S29&gt;T29,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1523,8 +1713,14 @@
       </c>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="3">
-        <f>IF(A30="","",IF(Q30=0,"Set a cap",IF(P30&gt;Q30,"Over cap - shrink batch","OK")))</f>
+      <c r="R30" s="4" t="n"/>
+      <c r="S30" s="5">
+        <f>IF(A30="","",P30+Q30+R30)</f>
+        <v/>
+      </c>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="3">
+        <f>IF(A30="","",IF(T30=0,"Set a cap",IF(S30&gt;T30,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1554,8 +1750,14 @@
       </c>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="3">
-        <f>IF(A31="","",IF(Q31=0,"Set a cap",IF(P31&gt;Q31,"Over cap - shrink batch","OK")))</f>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="5">
+        <f>IF(A31="","",P31+Q31+R31)</f>
+        <v/>
+      </c>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="3">
+        <f>IF(A31="","",IF(T31=0,"Set a cap",IF(S31&gt;T31,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1585,8 +1787,14 @@
       </c>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="3">
-        <f>IF(A32="","",IF(Q32=0,"Set a cap",IF(P32&gt;Q32,"Over cap - shrink batch","OK")))</f>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="5">
+        <f>IF(A32="","",P32+Q32+R32)</f>
+        <v/>
+      </c>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="3">
+        <f>IF(A32="","",IF(T32=0,"Set a cap",IF(S32&gt;T32,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1616,8 +1824,14 @@
       </c>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
-      <c r="R33" s="3">
-        <f>IF(A33="","",IF(Q33=0,"Set a cap",IF(P33&gt;Q33,"Over cap - shrink batch","OK")))</f>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="5">
+        <f>IF(A33="","",P33+Q33+R33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="3">
+        <f>IF(A33="","",IF(T33=0,"Set a cap",IF(S33&gt;T33,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1647,8 +1861,14 @@
       </c>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="3">
-        <f>IF(A34="","",IF(Q34=0,"Set a cap",IF(P34&gt;Q34,"Over cap - shrink batch","OK")))</f>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="5">
+        <f>IF(A34="","",P34+Q34+R34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="3">
+        <f>IF(A34="","",IF(T34=0,"Set a cap",IF(S34&gt;T34,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1678,8 +1898,14 @@
       </c>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="3">
-        <f>IF(A35="","",IF(Q35=0,"Set a cap",IF(P35&gt;Q35,"Over cap - shrink batch","OK")))</f>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="5">
+        <f>IF(A35="","",P35+Q35+R35)</f>
+        <v/>
+      </c>
+      <c r="T35" s="4" t="n"/>
+      <c r="U35" s="3">
+        <f>IF(A35="","",IF(T35=0,"Set a cap",IF(S35&gt;T35,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1709,8 +1935,14 @@
       </c>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="3">
-        <f>IF(A36="","",IF(Q36=0,"Set a cap",IF(P36&gt;Q36,"Over cap - shrink batch","OK")))</f>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="5">
+        <f>IF(A36="","",P36+Q36+R36)</f>
+        <v/>
+      </c>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="3">
+        <f>IF(A36="","",IF(T36=0,"Set a cap",IF(S36&gt;T36,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1740,8 +1972,14 @@
       </c>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="3">
-        <f>IF(A37="","",IF(Q37=0,"Set a cap",IF(P37&gt;Q37,"Over cap - shrink batch","OK")))</f>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="5">
+        <f>IF(A37="","",P37+Q37+R37)</f>
+        <v/>
+      </c>
+      <c r="T37" s="4" t="n"/>
+      <c r="U37" s="3">
+        <f>IF(A37="","",IF(T37=0,"Set a cap",IF(S37&gt;T37,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1771,8 +2009,14 @@
       </c>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="3">
-        <f>IF(A38="","",IF(Q38=0,"Set a cap",IF(P38&gt;Q38,"Over cap - shrink batch","OK")))</f>
+      <c r="R38" s="4" t="n"/>
+      <c r="S38" s="5">
+        <f>IF(A38="","",P38+Q38+R38)</f>
+        <v/>
+      </c>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="3">
+        <f>IF(A38="","",IF(T38=0,"Set a cap",IF(S38&gt;T38,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1802,8 +2046,14 @@
       </c>
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
-      <c r="R39" s="3">
-        <f>IF(A39="","",IF(Q39=0,"Set a cap",IF(P39&gt;Q39,"Over cap - shrink batch","OK")))</f>
+      <c r="R39" s="4" t="n"/>
+      <c r="S39" s="5">
+        <f>IF(A39="","",P39+Q39+R39)</f>
+        <v/>
+      </c>
+      <c r="T39" s="4" t="n"/>
+      <c r="U39" s="3">
+        <f>IF(A39="","",IF(T39=0,"Set a cap",IF(S39&gt;T39,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1833,8 +2083,14 @@
       </c>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
-      <c r="R40" s="3">
-        <f>IF(A40="","",IF(Q40=0,"Set a cap",IF(P40&gt;Q40,"Over cap - shrink batch","OK")))</f>
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="5">
+        <f>IF(A40="","",P40+Q40+R40)</f>
+        <v/>
+      </c>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="3">
+        <f>IF(A40="","",IF(T40=0,"Set a cap",IF(S40&gt;T40,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1864,8 +2120,14 @@
       </c>
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="n"/>
-      <c r="R41" s="3">
-        <f>IF(A41="","",IF(Q41=0,"Set a cap",IF(P41&gt;Q41,"Over cap - shrink batch","OK")))</f>
+      <c r="R41" s="4" t="n"/>
+      <c r="S41" s="5">
+        <f>IF(A41="","",P41+Q41+R41)</f>
+        <v/>
+      </c>
+      <c r="T41" s="4" t="n"/>
+      <c r="U41" s="3">
+        <f>IF(A41="","",IF(T41=0,"Set a cap",IF(S41&gt;T41,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1895,8 +2157,14 @@
       </c>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
-      <c r="R42" s="3">
-        <f>IF(A42="","",IF(Q42=0,"Set a cap",IF(P42&gt;Q42,"Over cap - shrink batch","OK")))</f>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="5">
+        <f>IF(A42="","",P42+Q42+R42)</f>
+        <v/>
+      </c>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="3">
+        <f>IF(A42="","",IF(T42=0,"Set a cap",IF(S42&gt;T42,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1926,8 +2194,14 @@
       </c>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="3">
-        <f>IF(A43="","",IF(Q43=0,"Set a cap",IF(P43&gt;Q43,"Over cap - shrink batch","OK")))</f>
+      <c r="R43" s="4" t="n"/>
+      <c r="S43" s="5">
+        <f>IF(A43="","",P43+Q43+R43)</f>
+        <v/>
+      </c>
+      <c r="T43" s="4" t="n"/>
+      <c r="U43" s="3">
+        <f>IF(A43="","",IF(T43=0,"Set a cap",IF(S43&gt;T43,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1957,8 +2231,14 @@
       </c>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
-      <c r="R44" s="3">
-        <f>IF(A44="","",IF(Q44=0,"Set a cap",IF(P44&gt;Q44,"Over cap - shrink batch","OK")))</f>
+      <c r="R44" s="4" t="n"/>
+      <c r="S44" s="5">
+        <f>IF(A44="","",P44+Q44+R44)</f>
+        <v/>
+      </c>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="3">
+        <f>IF(A44="","",IF(T44=0,"Set a cap",IF(S44&gt;T44,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1988,8 +2268,14 @@
       </c>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="3">
-        <f>IF(A45="","",IF(Q45=0,"Set a cap",IF(P45&gt;Q45,"Over cap - shrink batch","OK")))</f>
+      <c r="R45" s="4" t="n"/>
+      <c r="S45" s="5">
+        <f>IF(A45="","",P45+Q45+R45)</f>
+        <v/>
+      </c>
+      <c r="T45" s="4" t="n"/>
+      <c r="U45" s="3">
+        <f>IF(A45="","",IF(T45=0,"Set a cap",IF(S45&gt;T45,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2019,8 +2305,14 @@
       </c>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
-      <c r="R46" s="3">
-        <f>IF(A46="","",IF(Q46=0,"Set a cap",IF(P46&gt;Q46,"Over cap - shrink batch","OK")))</f>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="5">
+        <f>IF(A46="","",P46+Q46+R46)</f>
+        <v/>
+      </c>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="3">
+        <f>IF(A46="","",IF(T46=0,"Set a cap",IF(S46&gt;T46,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2050,8 +2342,14 @@
       </c>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="3">
-        <f>IF(A47="","",IF(Q47=0,"Set a cap",IF(P47&gt;Q47,"Over cap - shrink batch","OK")))</f>
+      <c r="R47" s="4" t="n"/>
+      <c r="S47" s="5">
+        <f>IF(A47="","",P47+Q47+R47)</f>
+        <v/>
+      </c>
+      <c r="T47" s="4" t="n"/>
+      <c r="U47" s="3">
+        <f>IF(A47="","",IF(T47=0,"Set a cap",IF(S47&gt;T47,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2081,8 +2379,14 @@
       </c>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="3">
-        <f>IF(A48="","",IF(Q48=0,"Set a cap",IF(P48&gt;Q48,"Over cap - shrink batch","OK")))</f>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="5">
+        <f>IF(A48="","",P48+Q48+R48)</f>
+        <v/>
+      </c>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="3">
+        <f>IF(A48="","",IF(T48=0,"Set a cap",IF(S48&gt;T48,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2112,8 +2416,14 @@
       </c>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
-      <c r="R49" s="3">
-        <f>IF(A49="","",IF(Q49=0,"Set a cap",IF(P49&gt;Q49,"Over cap - shrink batch","OK")))</f>
+      <c r="R49" s="4" t="n"/>
+      <c r="S49" s="5">
+        <f>IF(A49="","",P49+Q49+R49)</f>
+        <v/>
+      </c>
+      <c r="T49" s="4" t="n"/>
+      <c r="U49" s="3">
+        <f>IF(A49="","",IF(T49=0,"Set a cap",IF(S49&gt;T49,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2143,8 +2453,14 @@
       </c>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
-      <c r="R50" s="3">
-        <f>IF(A50="","",IF(Q50=0,"Set a cap",IF(P50&gt;Q50,"Over cap - shrink batch","OK")))</f>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="5">
+        <f>IF(A50="","",P50+Q50+R50)</f>
+        <v/>
+      </c>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="3">
+        <f>IF(A50="","",IF(T50=0,"Set a cap",IF(S50&gt;T50,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2174,8 +2490,14 @@
       </c>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
-      <c r="R51" s="3">
-        <f>IF(A51="","",IF(Q51=0,"Set a cap",IF(P51&gt;Q51,"Over cap - shrink batch","OK")))</f>
+      <c r="R51" s="4" t="n"/>
+      <c r="S51" s="5">
+        <f>IF(A51="","",P51+Q51+R51)</f>
+        <v/>
+      </c>
+      <c r="T51" s="4" t="n"/>
+      <c r="U51" s="3">
+        <f>IF(A51="","",IF(T51=0,"Set a cap",IF(S51&gt;T51,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2205,8 +2527,14 @@
       </c>
       <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="3">
-        <f>IF(A52="","",IF(Q52=0,"Set a cap",IF(P52&gt;Q52,"Over cap - shrink batch","OK")))</f>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="5">
+        <f>IF(A52="","",P52+Q52+R52)</f>
+        <v/>
+      </c>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="3">
+        <f>IF(A52="","",IF(T52=0,"Set a cap",IF(S52&gt;T52,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2236,8 +2564,14 @@
       </c>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
-      <c r="R53" s="3">
-        <f>IF(A53="","",IF(Q53=0,"Set a cap",IF(P53&gt;Q53,"Over cap - shrink batch","OK")))</f>
+      <c r="R53" s="4" t="n"/>
+      <c r="S53" s="5">
+        <f>IF(A53="","",P53+Q53+R53)</f>
+        <v/>
+      </c>
+      <c r="T53" s="4" t="n"/>
+      <c r="U53" s="3">
+        <f>IF(A53="","",IF(T53=0,"Set a cap",IF(S53&gt;T53,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2267,8 +2601,14 @@
       </c>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
-      <c r="R54" s="3">
-        <f>IF(A54="","",IF(Q54=0,"Set a cap",IF(P54&gt;Q54,"Over cap - shrink batch","OK")))</f>
+      <c r="R54" s="4" t="n"/>
+      <c r="S54" s="5">
+        <f>IF(A54="","",P54+Q54+R54)</f>
+        <v/>
+      </c>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="3">
+        <f>IF(A54="","",IF(T54=0,"Set a cap",IF(S54&gt;T54,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2298,8 +2638,14 @@
       </c>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
-      <c r="R55" s="3">
-        <f>IF(A55="","",IF(Q55=0,"Set a cap",IF(P55&gt;Q55,"Over cap - shrink batch","OK")))</f>
+      <c r="R55" s="4" t="n"/>
+      <c r="S55" s="5">
+        <f>IF(A55="","",P55+Q55+R55)</f>
+        <v/>
+      </c>
+      <c r="T55" s="4" t="n"/>
+      <c r="U55" s="3">
+        <f>IF(A55="","",IF(T55=0,"Set a cap",IF(S55&gt;T55,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2329,8 +2675,14 @@
       </c>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
-      <c r="R56" s="3">
-        <f>IF(A56="","",IF(Q56=0,"Set a cap",IF(P56&gt;Q56,"Over cap - shrink batch","OK")))</f>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="5">
+        <f>IF(A56="","",P56+Q56+R56)</f>
+        <v/>
+      </c>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="3">
+        <f>IF(A56="","",IF(T56=0,"Set a cap",IF(S56&gt;T56,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2360,8 +2712,14 @@
       </c>
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="3">
-        <f>IF(A57="","",IF(Q57=0,"Set a cap",IF(P57&gt;Q57,"Over cap - shrink batch","OK")))</f>
+      <c r="R57" s="4" t="n"/>
+      <c r="S57" s="5">
+        <f>IF(A57="","",P57+Q57+R57)</f>
+        <v/>
+      </c>
+      <c r="T57" s="4" t="n"/>
+      <c r="U57" s="3">
+        <f>IF(A57="","",IF(T57=0,"Set a cap",IF(S57&gt;T57,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2391,8 +2749,14 @@
       </c>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
-      <c r="R58" s="3">
-        <f>IF(A58="","",IF(Q58=0,"Set a cap",IF(P58&gt;Q58,"Over cap - shrink batch","OK")))</f>
+      <c r="R58" s="4" t="n"/>
+      <c r="S58" s="5">
+        <f>IF(A58="","",P58+Q58+R58)</f>
+        <v/>
+      </c>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="3">
+        <f>IF(A58="","",IF(T58=0,"Set a cap",IF(S58&gt;T58,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2422,8 +2786,14 @@
       </c>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
-      <c r="R59" s="3">
-        <f>IF(A59="","",IF(Q59=0,"Set a cap",IF(P59&gt;Q59,"Over cap - shrink batch","OK")))</f>
+      <c r="R59" s="4" t="n"/>
+      <c r="S59" s="5">
+        <f>IF(A59="","",P59+Q59+R59)</f>
+        <v/>
+      </c>
+      <c r="T59" s="4" t="n"/>
+      <c r="U59" s="3">
+        <f>IF(A59="","",IF(T59=0,"Set a cap",IF(S59&gt;T59,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2453,8 +2823,14 @@
       </c>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="3">
-        <f>IF(A60="","",IF(Q60=0,"Set a cap",IF(P60&gt;Q60,"Over cap - shrink batch","OK")))</f>
+      <c r="R60" s="4" t="n"/>
+      <c r="S60" s="5">
+        <f>IF(A60="","",P60+Q60+R60)</f>
+        <v/>
+      </c>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="3">
+        <f>IF(A60="","",IF(T60=0,"Set a cap",IF(S60&gt;T60,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2484,8 +2860,14 @@
       </c>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
-      <c r="R61" s="3">
-        <f>IF(A61="","",IF(Q61=0,"Set a cap",IF(P61&gt;Q61,"Over cap - shrink batch","OK")))</f>
+      <c r="R61" s="4" t="n"/>
+      <c r="S61" s="5">
+        <f>IF(A61="","",P61+Q61+R61)</f>
+        <v/>
+      </c>
+      <c r="T61" s="4" t="n"/>
+      <c r="U61" s="3">
+        <f>IF(A61="","",IF(T61=0,"Set a cap",IF(S61&gt;T61,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2515,8 +2897,14 @@
       </c>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
-      <c r="R62" s="3">
-        <f>IF(A62="","",IF(Q62=0,"Set a cap",IF(P62&gt;Q62,"Over cap - shrink batch","OK")))</f>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="5">
+        <f>IF(A62="","",P62+Q62+R62)</f>
+        <v/>
+      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="3">
+        <f>IF(A62="","",IF(T62=0,"Set a cap",IF(S62&gt;T62,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2546,8 +2934,14 @@
       </c>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="3">
-        <f>IF(A63="","",IF(Q63=0,"Set a cap",IF(P63&gt;Q63,"Over cap - shrink batch","OK")))</f>
+      <c r="R63" s="4" t="n"/>
+      <c r="S63" s="5">
+        <f>IF(A63="","",P63+Q63+R63)</f>
+        <v/>
+      </c>
+      <c r="T63" s="4" t="n"/>
+      <c r="U63" s="3">
+        <f>IF(A63="","",IF(T63=0,"Set a cap",IF(S63&gt;T63,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2577,8 +2971,14 @@
       </c>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
-      <c r="R64" s="3">
-        <f>IF(A64="","",IF(Q64=0,"Set a cap",IF(P64&gt;Q64,"Over cap - shrink batch","OK")))</f>
+      <c r="R64" s="4" t="n"/>
+      <c r="S64" s="5">
+        <f>IF(A64="","",P64+Q64+R64)</f>
+        <v/>
+      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="3">
+        <f>IF(A64="","",IF(T64=0,"Set a cap",IF(S64&gt;T64,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2608,8 +3008,14 @@
       </c>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
-      <c r="R65" s="3">
-        <f>IF(A65="","",IF(Q65=0,"Set a cap",IF(P65&gt;Q65,"Over cap - shrink batch","OK")))</f>
+      <c r="R65" s="4" t="n"/>
+      <c r="S65" s="5">
+        <f>IF(A65="","",P65+Q65+R65)</f>
+        <v/>
+      </c>
+      <c r="T65" s="4" t="n"/>
+      <c r="U65" s="3">
+        <f>IF(A65="","",IF(T65=0,"Set a cap",IF(S65&gt;T65,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2639,8 +3045,14 @@
       </c>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
-      <c r="R66" s="3">
-        <f>IF(A66="","",IF(Q66=0,"Set a cap",IF(P66&gt;Q66,"Over cap - shrink batch","OK")))</f>
+      <c r="R66" s="4" t="n"/>
+      <c r="S66" s="5">
+        <f>IF(A66="","",P66+Q66+R66)</f>
+        <v/>
+      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="3">
+        <f>IF(A66="","",IF(T66=0,"Set a cap",IF(S66&gt;T66,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2670,8 +3082,14 @@
       </c>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="3">
-        <f>IF(A67="","",IF(Q67=0,"Set a cap",IF(P67&gt;Q67,"Over cap - shrink batch","OK")))</f>
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="5">
+        <f>IF(A67="","",P67+Q67+R67)</f>
+        <v/>
+      </c>
+      <c r="T67" s="4" t="n"/>
+      <c r="U67" s="3">
+        <f>IF(A67="","",IF(T67=0,"Set a cap",IF(S67&gt;T67,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2701,8 +3119,14 @@
       </c>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
-      <c r="R68" s="3">
-        <f>IF(A68="","",IF(Q68=0,"Set a cap",IF(P68&gt;Q68,"Over cap - shrink batch","OK")))</f>
+      <c r="R68" s="4" t="n"/>
+      <c r="S68" s="5">
+        <f>IF(A68="","",P68+Q68+R68)</f>
+        <v/>
+      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="3">
+        <f>IF(A68="","",IF(T68=0,"Set a cap",IF(S68&gt;T68,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2732,8 +3156,14 @@
       </c>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="3">
-        <f>IF(A69="","",IF(Q69=0,"Set a cap",IF(P69&gt;Q69,"Over cap - shrink batch","OK")))</f>
+      <c r="R69" s="4" t="n"/>
+      <c r="S69" s="5">
+        <f>IF(A69="","",P69+Q69+R69)</f>
+        <v/>
+      </c>
+      <c r="T69" s="4" t="n"/>
+      <c r="U69" s="3">
+        <f>IF(A69="","",IF(T69=0,"Set a cap",IF(S69&gt;T69,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2763,8 +3193,14 @@
       </c>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
-      <c r="R70" s="3">
-        <f>IF(A70="","",IF(Q70=0,"Set a cap",IF(P70&gt;Q70,"Over cap - shrink batch","OK")))</f>
+      <c r="R70" s="4" t="n"/>
+      <c r="S70" s="5">
+        <f>IF(A70="","",P70+Q70+R70)</f>
+        <v/>
+      </c>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="3">
+        <f>IF(A70="","",IF(T70=0,"Set a cap",IF(S70&gt;T70,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2794,8 +3230,14 @@
       </c>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
-      <c r="R71" s="3">
-        <f>IF(A71="","",IF(Q71=0,"Set a cap",IF(P71&gt;Q71,"Over cap - shrink batch","OK")))</f>
+      <c r="R71" s="4" t="n"/>
+      <c r="S71" s="5">
+        <f>IF(A71="","",P71+Q71+R71)</f>
+        <v/>
+      </c>
+      <c r="T71" s="4" t="n"/>
+      <c r="U71" s="3">
+        <f>IF(A71="","",IF(T71=0,"Set a cap",IF(S71&gt;T71,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2825,8 +3267,14 @@
       </c>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
-      <c r="R72" s="3">
-        <f>IF(A72="","",IF(Q72=0,"Set a cap",IF(P72&gt;Q72,"Over cap - shrink batch","OK")))</f>
+      <c r="R72" s="4" t="n"/>
+      <c r="S72" s="5">
+        <f>IF(A72="","",P72+Q72+R72)</f>
+        <v/>
+      </c>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="3">
+        <f>IF(A72="","",IF(T72=0,"Set a cap",IF(S72&gt;T72,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2856,8 +3304,14 @@
       </c>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
-      <c r="R73" s="3">
-        <f>IF(A73="","",IF(Q73=0,"Set a cap",IF(P73&gt;Q73,"Over cap - shrink batch","OK")))</f>
+      <c r="R73" s="4" t="n"/>
+      <c r="S73" s="5">
+        <f>IF(A73="","",P73+Q73+R73)</f>
+        <v/>
+      </c>
+      <c r="T73" s="4" t="n"/>
+      <c r="U73" s="3">
+        <f>IF(A73="","",IF(T73=0,"Set a cap",IF(S73&gt;T73,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2887,8 +3341,14 @@
       </c>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
-      <c r="R74" s="3">
-        <f>IF(A74="","",IF(Q74=0,"Set a cap",IF(P74&gt;Q74,"Over cap - shrink batch","OK")))</f>
+      <c r="R74" s="4" t="n"/>
+      <c r="S74" s="5">
+        <f>IF(A74="","",P74+Q74+R74)</f>
+        <v/>
+      </c>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="3">
+        <f>IF(A74="","",IF(T74=0,"Set a cap",IF(S74&gt;T74,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2918,8 +3378,14 @@
       </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="3">
-        <f>IF(A75="","",IF(Q75=0,"Set a cap",IF(P75&gt;Q75,"Over cap - shrink batch","OK")))</f>
+      <c r="R75" s="4" t="n"/>
+      <c r="S75" s="5">
+        <f>IF(A75="","",P75+Q75+R75)</f>
+        <v/>
+      </c>
+      <c r="T75" s="4" t="n"/>
+      <c r="U75" s="3">
+        <f>IF(A75="","",IF(T75=0,"Set a cap",IF(S75&gt;T75,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2949,8 +3415,14 @@
       </c>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="3">
-        <f>IF(A76="","",IF(Q76=0,"Set a cap",IF(P76&gt;Q76,"Over cap - shrink batch","OK")))</f>
+      <c r="R76" s="4" t="n"/>
+      <c r="S76" s="5">
+        <f>IF(A76="","",P76+Q76+R76)</f>
+        <v/>
+      </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="3">
+        <f>IF(A76="","",IF(T76=0,"Set a cap",IF(S76&gt;T76,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -2980,8 +3452,14 @@
       </c>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
-      <c r="R77" s="3">
-        <f>IF(A77="","",IF(Q77=0,"Set a cap",IF(P77&gt;Q77,"Over cap - shrink batch","OK")))</f>
+      <c r="R77" s="4" t="n"/>
+      <c r="S77" s="5">
+        <f>IF(A77="","",P77+Q77+R77)</f>
+        <v/>
+      </c>
+      <c r="T77" s="4" t="n"/>
+      <c r="U77" s="3">
+        <f>IF(A77="","",IF(T77=0,"Set a cap",IF(S77&gt;T77,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3011,8 +3489,14 @@
       </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
-      <c r="R78" s="3">
-        <f>IF(A78="","",IF(Q78=0,"Set a cap",IF(P78&gt;Q78,"Over cap - shrink batch","OK")))</f>
+      <c r="R78" s="4" t="n"/>
+      <c r="S78" s="5">
+        <f>IF(A78="","",P78+Q78+R78)</f>
+        <v/>
+      </c>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="3">
+        <f>IF(A78="","",IF(T78=0,"Set a cap",IF(S78&gt;T78,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3042,8 +3526,14 @@
       </c>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
-      <c r="R79" s="3">
-        <f>IF(A79="","",IF(Q79=0,"Set a cap",IF(P79&gt;Q79,"Over cap - shrink batch","OK")))</f>
+      <c r="R79" s="4" t="n"/>
+      <c r="S79" s="5">
+        <f>IF(A79="","",P79+Q79+R79)</f>
+        <v/>
+      </c>
+      <c r="T79" s="4" t="n"/>
+      <c r="U79" s="3">
+        <f>IF(A79="","",IF(T79=0,"Set a cap",IF(S79&gt;T79,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3073,8 +3563,14 @@
       </c>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
-      <c r="R80" s="3">
-        <f>IF(A80="","",IF(Q80=0,"Set a cap",IF(P80&gt;Q80,"Over cap - shrink batch","OK")))</f>
+      <c r="R80" s="4" t="n"/>
+      <c r="S80" s="5">
+        <f>IF(A80="","",P80+Q80+R80)</f>
+        <v/>
+      </c>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="3">
+        <f>IF(A80="","",IF(T80=0,"Set a cap",IF(S80&gt;T80,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3104,8 +3600,14 @@
       </c>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
-      <c r="R81" s="3">
-        <f>IF(A81="","",IF(Q81=0,"Set a cap",IF(P81&gt;Q81,"Over cap - shrink batch","OK")))</f>
+      <c r="R81" s="4" t="n"/>
+      <c r="S81" s="5">
+        <f>IF(A81="","",P81+Q81+R81)</f>
+        <v/>
+      </c>
+      <c r="T81" s="4" t="n"/>
+      <c r="U81" s="3">
+        <f>IF(A81="","",IF(T81=0,"Set a cap",IF(S81&gt;T81,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3135,8 +3637,14 @@
       </c>
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
-      <c r="R82" s="3">
-        <f>IF(A82="","",IF(Q82=0,"Set a cap",IF(P82&gt;Q82,"Over cap - shrink batch","OK")))</f>
+      <c r="R82" s="4" t="n"/>
+      <c r="S82" s="5">
+        <f>IF(A82="","",P82+Q82+R82)</f>
+        <v/>
+      </c>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="3">
+        <f>IF(A82="","",IF(T82=0,"Set a cap",IF(S82&gt;T82,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3166,8 +3674,14 @@
       </c>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
-      <c r="R83" s="3">
-        <f>IF(A83="","",IF(Q83=0,"Set a cap",IF(P83&gt;Q83,"Over cap - shrink batch","OK")))</f>
+      <c r="R83" s="4" t="n"/>
+      <c r="S83" s="5">
+        <f>IF(A83="","",P83+Q83+R83)</f>
+        <v/>
+      </c>
+      <c r="T83" s="4" t="n"/>
+      <c r="U83" s="3">
+        <f>IF(A83="","",IF(T83=0,"Set a cap",IF(S83&gt;T83,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3197,8 +3711,14 @@
       </c>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
-      <c r="R84" s="3">
-        <f>IF(A84="","",IF(Q84=0,"Set a cap",IF(P84&gt;Q84,"Over cap - shrink batch","OK")))</f>
+      <c r="R84" s="4" t="n"/>
+      <c r="S84" s="5">
+        <f>IF(A84="","",P84+Q84+R84)</f>
+        <v/>
+      </c>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="3">
+        <f>IF(A84="","",IF(T84=0,"Set a cap",IF(S84&gt;T84,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3228,8 +3748,14 @@
       </c>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
-      <c r="R85" s="3">
-        <f>IF(A85="","",IF(Q85=0,"Set a cap",IF(P85&gt;Q85,"Over cap - shrink batch","OK")))</f>
+      <c r="R85" s="4" t="n"/>
+      <c r="S85" s="5">
+        <f>IF(A85="","",P85+Q85+R85)</f>
+        <v/>
+      </c>
+      <c r="T85" s="4" t="n"/>
+      <c r="U85" s="3">
+        <f>IF(A85="","",IF(T85=0,"Set a cap",IF(S85&gt;T85,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3259,8 +3785,14 @@
       </c>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
-      <c r="R86" s="3">
-        <f>IF(A86="","",IF(Q86=0,"Set a cap",IF(P86&gt;Q86,"Over cap - shrink batch","OK")))</f>
+      <c r="R86" s="4" t="n"/>
+      <c r="S86" s="5">
+        <f>IF(A86="","",P86+Q86+R86)</f>
+        <v/>
+      </c>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="3">
+        <f>IF(A86="","",IF(T86=0,"Set a cap",IF(S86&gt;T86,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3290,8 +3822,14 @@
       </c>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
-      <c r="R87" s="3">
-        <f>IF(A87="","",IF(Q87=0,"Set a cap",IF(P87&gt;Q87,"Over cap - shrink batch","OK")))</f>
+      <c r="R87" s="4" t="n"/>
+      <c r="S87" s="5">
+        <f>IF(A87="","",P87+Q87+R87)</f>
+        <v/>
+      </c>
+      <c r="T87" s="4" t="n"/>
+      <c r="U87" s="3">
+        <f>IF(A87="","",IF(T87=0,"Set a cap",IF(S87&gt;T87,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3321,8 +3859,14 @@
       </c>
       <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
-      <c r="R88" s="3">
-        <f>IF(A88="","",IF(Q88=0,"Set a cap",IF(P88&gt;Q88,"Over cap - shrink batch","OK")))</f>
+      <c r="R88" s="4" t="n"/>
+      <c r="S88" s="5">
+        <f>IF(A88="","",P88+Q88+R88)</f>
+        <v/>
+      </c>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="3">
+        <f>IF(A88="","",IF(T88=0,"Set a cap",IF(S88&gt;T88,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3352,8 +3896,14 @@
       </c>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
-      <c r="R89" s="3">
-        <f>IF(A89="","",IF(Q89=0,"Set a cap",IF(P89&gt;Q89,"Over cap - shrink batch","OK")))</f>
+      <c r="R89" s="4" t="n"/>
+      <c r="S89" s="5">
+        <f>IF(A89="","",P89+Q89+R89)</f>
+        <v/>
+      </c>
+      <c r="T89" s="4" t="n"/>
+      <c r="U89" s="3">
+        <f>IF(A89="","",IF(T89=0,"Set a cap",IF(S89&gt;T89,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3383,8 +3933,14 @@
       </c>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
-      <c r="R90" s="3">
-        <f>IF(A90="","",IF(Q90=0,"Set a cap",IF(P90&gt;Q90,"Over cap - shrink batch","OK")))</f>
+      <c r="R90" s="4" t="n"/>
+      <c r="S90" s="5">
+        <f>IF(A90="","",P90+Q90+R90)</f>
+        <v/>
+      </c>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="3">
+        <f>IF(A90="","",IF(T90=0,"Set a cap",IF(S90&gt;T90,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3414,8 +3970,14 @@
       </c>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
-      <c r="R91" s="3">
-        <f>IF(A91="","",IF(Q91=0,"Set a cap",IF(P91&gt;Q91,"Over cap - shrink batch","OK")))</f>
+      <c r="R91" s="4" t="n"/>
+      <c r="S91" s="5">
+        <f>IF(A91="","",P91+Q91+R91)</f>
+        <v/>
+      </c>
+      <c r="T91" s="4" t="n"/>
+      <c r="U91" s="3">
+        <f>IF(A91="","",IF(T91=0,"Set a cap",IF(S91&gt;T91,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3445,8 +4007,14 @@
       </c>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
-      <c r="R92" s="3">
-        <f>IF(A92="","",IF(Q92=0,"Set a cap",IF(P92&gt;Q92,"Over cap - shrink batch","OK")))</f>
+      <c r="R92" s="4" t="n"/>
+      <c r="S92" s="5">
+        <f>IF(A92="","",P92+Q92+R92)</f>
+        <v/>
+      </c>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="3">
+        <f>IF(A92="","",IF(T92=0,"Set a cap",IF(S92&gt;T92,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3476,8 +4044,14 @@
       </c>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
-      <c r="R93" s="3">
-        <f>IF(A93="","",IF(Q93=0,"Set a cap",IF(P93&gt;Q93,"Over cap - shrink batch","OK")))</f>
+      <c r="R93" s="4" t="n"/>
+      <c r="S93" s="5">
+        <f>IF(A93="","",P93+Q93+R93)</f>
+        <v/>
+      </c>
+      <c r="T93" s="4" t="n"/>
+      <c r="U93" s="3">
+        <f>IF(A93="","",IF(T93=0,"Set a cap",IF(S93&gt;T93,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3507,8 +4081,14 @@
       </c>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
-      <c r="R94" s="3">
-        <f>IF(A94="","",IF(Q94=0,"Set a cap",IF(P94&gt;Q94,"Over cap - shrink batch","OK")))</f>
+      <c r="R94" s="4" t="n"/>
+      <c r="S94" s="5">
+        <f>IF(A94="","",P94+Q94+R94)</f>
+        <v/>
+      </c>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="3">
+        <f>IF(A94="","",IF(T94=0,"Set a cap",IF(S94&gt;T94,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3538,8 +4118,14 @@
       </c>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
-      <c r="R95" s="3">
-        <f>IF(A95="","",IF(Q95=0,"Set a cap",IF(P95&gt;Q95,"Over cap - shrink batch","OK")))</f>
+      <c r="R95" s="4" t="n"/>
+      <c r="S95" s="5">
+        <f>IF(A95="","",P95+Q95+R95)</f>
+        <v/>
+      </c>
+      <c r="T95" s="4" t="n"/>
+      <c r="U95" s="3">
+        <f>IF(A95="","",IF(T95=0,"Set a cap",IF(S95&gt;T95,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3569,8 +4155,14 @@
       </c>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
-      <c r="R96" s="3">
-        <f>IF(A96="","",IF(Q96=0,"Set a cap",IF(P96&gt;Q96,"Over cap - shrink batch","OK")))</f>
+      <c r="R96" s="4" t="n"/>
+      <c r="S96" s="5">
+        <f>IF(A96="","",P96+Q96+R96)</f>
+        <v/>
+      </c>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="3">
+        <f>IF(A96="","",IF(T96=0,"Set a cap",IF(S96&gt;T96,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3600,8 +4192,14 @@
       </c>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
-      <c r="R97" s="3">
-        <f>IF(A97="","",IF(Q97=0,"Set a cap",IF(P97&gt;Q97,"Over cap - shrink batch","OK")))</f>
+      <c r="R97" s="4" t="n"/>
+      <c r="S97" s="5">
+        <f>IF(A97="","",P97+Q97+R97)</f>
+        <v/>
+      </c>
+      <c r="T97" s="4" t="n"/>
+      <c r="U97" s="3">
+        <f>IF(A97="","",IF(T97=0,"Set a cap",IF(S97&gt;T97,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3631,8 +4229,14 @@
       </c>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
-      <c r="R98" s="3">
-        <f>IF(A98="","",IF(Q98=0,"Set a cap",IF(P98&gt;Q98,"Over cap - shrink batch","OK")))</f>
+      <c r="R98" s="4" t="n"/>
+      <c r="S98" s="5">
+        <f>IF(A98="","",P98+Q98+R98)</f>
+        <v/>
+      </c>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="3">
+        <f>IF(A98="","",IF(T98=0,"Set a cap",IF(S98&gt;T98,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3662,8 +4266,14 @@
       </c>
       <c r="P99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
-      <c r="R99" s="3">
-        <f>IF(A99="","",IF(Q99=0,"Set a cap",IF(P99&gt;Q99,"Over cap - shrink batch","OK")))</f>
+      <c r="R99" s="4" t="n"/>
+      <c r="S99" s="5">
+        <f>IF(A99="","",P99+Q99+R99)</f>
+        <v/>
+      </c>
+      <c r="T99" s="4" t="n"/>
+      <c r="U99" s="3">
+        <f>IF(A99="","",IF(T99=0,"Set a cap",IF(S99&gt;T99,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3693,8 +4303,14 @@
       </c>
       <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
-      <c r="R100" s="3">
-        <f>IF(A100="","",IF(Q100=0,"Set a cap",IF(P100&gt;Q100,"Over cap - shrink batch","OK")))</f>
+      <c r="R100" s="4" t="n"/>
+      <c r="S100" s="5">
+        <f>IF(A100="","",P100+Q100+R100)</f>
+        <v/>
+      </c>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="3">
+        <f>IF(A100="","",IF(T100=0,"Set a cap",IF(S100&gt;T100,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3724,8 +4340,14 @@
       </c>
       <c r="P101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
-      <c r="R101" s="3">
-        <f>IF(A101="","",IF(Q101=0,"Set a cap",IF(P101&gt;Q101,"Over cap - shrink batch","OK")))</f>
+      <c r="R101" s="4" t="n"/>
+      <c r="S101" s="5">
+        <f>IF(A101="","",P101+Q101+R101)</f>
+        <v/>
+      </c>
+      <c r="T101" s="4" t="n"/>
+      <c r="U101" s="3">
+        <f>IF(A101="","",IF(T101=0,"Set a cap",IF(S101&gt;T101,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3755,8 +4377,14 @@
       </c>
       <c r="P102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
-      <c r="R102" s="3">
-        <f>IF(A102="","",IF(Q102=0,"Set a cap",IF(P102&gt;Q102,"Over cap - shrink batch","OK")))</f>
+      <c r="R102" s="4" t="n"/>
+      <c r="S102" s="5">
+        <f>IF(A102="","",P102+Q102+R102)</f>
+        <v/>
+      </c>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="3">
+        <f>IF(A102="","",IF(T102=0,"Set a cap",IF(S102&gt;T102,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3786,8 +4414,14 @@
       </c>
       <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
-      <c r="R103" s="3">
-        <f>IF(A103="","",IF(Q103=0,"Set a cap",IF(P103&gt;Q103,"Over cap - shrink batch","OK")))</f>
+      <c r="R103" s="4" t="n"/>
+      <c r="S103" s="5">
+        <f>IF(A103="","",P103+Q103+R103)</f>
+        <v/>
+      </c>
+      <c r="T103" s="4" t="n"/>
+      <c r="U103" s="3">
+        <f>IF(A103="","",IF(T103=0,"Set a cap",IF(S103&gt;T103,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3817,8 +4451,14 @@
       </c>
       <c r="P104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
-      <c r="R104" s="3">
-        <f>IF(A104="","",IF(Q104=0,"Set a cap",IF(P104&gt;Q104,"Over cap - shrink batch","OK")))</f>
+      <c r="R104" s="4" t="n"/>
+      <c r="S104" s="5">
+        <f>IF(A104="","",P104+Q104+R104)</f>
+        <v/>
+      </c>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="3">
+        <f>IF(A104="","",IF(T104=0,"Set a cap",IF(S104&gt;T104,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3848,8 +4488,14 @@
       </c>
       <c r="P105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
-      <c r="R105" s="3">
-        <f>IF(A105="","",IF(Q105=0,"Set a cap",IF(P105&gt;Q105,"Over cap - shrink batch","OK")))</f>
+      <c r="R105" s="4" t="n"/>
+      <c r="S105" s="5">
+        <f>IF(A105="","",P105+Q105+R105)</f>
+        <v/>
+      </c>
+      <c r="T105" s="4" t="n"/>
+      <c r="U105" s="3">
+        <f>IF(A105="","",IF(T105=0,"Set a cap",IF(S105&gt;T105,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3879,8 +4525,14 @@
       </c>
       <c r="P106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
-      <c r="R106" s="3">
-        <f>IF(A106="","",IF(Q106=0,"Set a cap",IF(P106&gt;Q106,"Over cap - shrink batch","OK")))</f>
+      <c r="R106" s="4" t="n"/>
+      <c r="S106" s="5">
+        <f>IF(A106="","",P106+Q106+R106)</f>
+        <v/>
+      </c>
+      <c r="T106" s="4" t="n"/>
+      <c r="U106" s="3">
+        <f>IF(A106="","",IF(T106=0,"Set a cap",IF(S106&gt;T106,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3910,8 +4562,14 @@
       </c>
       <c r="P107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
-      <c r="R107" s="3">
-        <f>IF(A107="","",IF(Q107=0,"Set a cap",IF(P107&gt;Q107,"Over cap - shrink batch","OK")))</f>
+      <c r="R107" s="4" t="n"/>
+      <c r="S107" s="5">
+        <f>IF(A107="","",P107+Q107+R107)</f>
+        <v/>
+      </c>
+      <c r="T107" s="4" t="n"/>
+      <c r="U107" s="3">
+        <f>IF(A107="","",IF(T107=0,"Set a cap",IF(S107&gt;T107,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3941,8 +4599,14 @@
       </c>
       <c r="P108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
-      <c r="R108" s="3">
-        <f>IF(A108="","",IF(Q108=0,"Set a cap",IF(P108&gt;Q108,"Over cap - shrink batch","OK")))</f>
+      <c r="R108" s="4" t="n"/>
+      <c r="S108" s="5">
+        <f>IF(A108="","",P108+Q108+R108)</f>
+        <v/>
+      </c>
+      <c r="T108" s="4" t="n"/>
+      <c r="U108" s="3">
+        <f>IF(A108="","",IF(T108=0,"Set a cap",IF(S108&gt;T108,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -3972,8 +4636,14 @@
       </c>
       <c r="P109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
-      <c r="R109" s="3">
-        <f>IF(A109="","",IF(Q109=0,"Set a cap",IF(P109&gt;Q109,"Over cap - shrink batch","OK")))</f>
+      <c r="R109" s="4" t="n"/>
+      <c r="S109" s="5">
+        <f>IF(A109="","",P109+Q109+R109)</f>
+        <v/>
+      </c>
+      <c r="T109" s="4" t="n"/>
+      <c r="U109" s="3">
+        <f>IF(A109="","",IF(T109=0,"Set a cap",IF(S109&gt;T109,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4003,8 +4673,14 @@
       </c>
       <c r="P110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
-      <c r="R110" s="3">
-        <f>IF(A110="","",IF(Q110=0,"Set a cap",IF(P110&gt;Q110,"Over cap - shrink batch","OK")))</f>
+      <c r="R110" s="4" t="n"/>
+      <c r="S110" s="5">
+        <f>IF(A110="","",P110+Q110+R110)</f>
+        <v/>
+      </c>
+      <c r="T110" s="4" t="n"/>
+      <c r="U110" s="3">
+        <f>IF(A110="","",IF(T110=0,"Set a cap",IF(S110&gt;T110,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4034,8 +4710,14 @@
       </c>
       <c r="P111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
-      <c r="R111" s="3">
-        <f>IF(A111="","",IF(Q111=0,"Set a cap",IF(P111&gt;Q111,"Over cap - shrink batch","OK")))</f>
+      <c r="R111" s="4" t="n"/>
+      <c r="S111" s="5">
+        <f>IF(A111="","",P111+Q111+R111)</f>
+        <v/>
+      </c>
+      <c r="T111" s="4" t="n"/>
+      <c r="U111" s="3">
+        <f>IF(A111="","",IF(T111=0,"Set a cap",IF(S111&gt;T111,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4065,8 +4747,14 @@
       </c>
       <c r="P112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
-      <c r="R112" s="3">
-        <f>IF(A112="","",IF(Q112=0,"Set a cap",IF(P112&gt;Q112,"Over cap - shrink batch","OK")))</f>
+      <c r="R112" s="4" t="n"/>
+      <c r="S112" s="5">
+        <f>IF(A112="","",P112+Q112+R112)</f>
+        <v/>
+      </c>
+      <c r="T112" s="4" t="n"/>
+      <c r="U112" s="3">
+        <f>IF(A112="","",IF(T112=0,"Set a cap",IF(S112&gt;T112,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4096,8 +4784,14 @@
       </c>
       <c r="P113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
-      <c r="R113" s="3">
-        <f>IF(A113="","",IF(Q113=0,"Set a cap",IF(P113&gt;Q113,"Over cap - shrink batch","OK")))</f>
+      <c r="R113" s="4" t="n"/>
+      <c r="S113" s="5">
+        <f>IF(A113="","",P113+Q113+R113)</f>
+        <v/>
+      </c>
+      <c r="T113" s="4" t="n"/>
+      <c r="U113" s="3">
+        <f>IF(A113="","",IF(T113=0,"Set a cap",IF(S113&gt;T113,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4127,8 +4821,14 @@
       </c>
       <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
-      <c r="R114" s="3">
-        <f>IF(A114="","",IF(Q114=0,"Set a cap",IF(P114&gt;Q114,"Over cap - shrink batch","OK")))</f>
+      <c r="R114" s="4" t="n"/>
+      <c r="S114" s="5">
+        <f>IF(A114="","",P114+Q114+R114)</f>
+        <v/>
+      </c>
+      <c r="T114" s="4" t="n"/>
+      <c r="U114" s="3">
+        <f>IF(A114="","",IF(T114=0,"Set a cap",IF(S114&gt;T114,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4158,8 +4858,14 @@
       </c>
       <c r="P115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
-      <c r="R115" s="3">
-        <f>IF(A115="","",IF(Q115=0,"Set a cap",IF(P115&gt;Q115,"Over cap - shrink batch","OK")))</f>
+      <c r="R115" s="4" t="n"/>
+      <c r="S115" s="5">
+        <f>IF(A115="","",P115+Q115+R115)</f>
+        <v/>
+      </c>
+      <c r="T115" s="4" t="n"/>
+      <c r="U115" s="3">
+        <f>IF(A115="","",IF(T115=0,"Set a cap",IF(S115&gt;T115,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4189,8 +4895,14 @@
       </c>
       <c r="P116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
-      <c r="R116" s="3">
-        <f>IF(A116="","",IF(Q116=0,"Set a cap",IF(P116&gt;Q116,"Over cap - shrink batch","OK")))</f>
+      <c r="R116" s="4" t="n"/>
+      <c r="S116" s="5">
+        <f>IF(A116="","",P116+Q116+R116)</f>
+        <v/>
+      </c>
+      <c r="T116" s="4" t="n"/>
+      <c r="U116" s="3">
+        <f>IF(A116="","",IF(T116=0,"Set a cap",IF(S116&gt;T116,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4220,8 +4932,14 @@
       </c>
       <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
-      <c r="R117" s="3">
-        <f>IF(A117="","",IF(Q117=0,"Set a cap",IF(P117&gt;Q117,"Over cap - shrink batch","OK")))</f>
+      <c r="R117" s="4" t="n"/>
+      <c r="S117" s="5">
+        <f>IF(A117="","",P117+Q117+R117)</f>
+        <v/>
+      </c>
+      <c r="T117" s="4" t="n"/>
+      <c r="U117" s="3">
+        <f>IF(A117="","",IF(T117=0,"Set a cap",IF(S117&gt;T117,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4251,8 +4969,14 @@
       </c>
       <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
-      <c r="R118" s="3">
-        <f>IF(A118="","",IF(Q118=0,"Set a cap",IF(P118&gt;Q118,"Over cap - shrink batch","OK")))</f>
+      <c r="R118" s="4" t="n"/>
+      <c r="S118" s="5">
+        <f>IF(A118="","",P118+Q118+R118)</f>
+        <v/>
+      </c>
+      <c r="T118" s="4" t="n"/>
+      <c r="U118" s="3">
+        <f>IF(A118="","",IF(T118=0,"Set a cap",IF(S118&gt;T118,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4282,8 +5006,14 @@
       </c>
       <c r="P119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
-      <c r="R119" s="3">
-        <f>IF(A119="","",IF(Q119=0,"Set a cap",IF(P119&gt;Q119,"Over cap - shrink batch","OK")))</f>
+      <c r="R119" s="4" t="n"/>
+      <c r="S119" s="5">
+        <f>IF(A119="","",P119+Q119+R119)</f>
+        <v/>
+      </c>
+      <c r="T119" s="4" t="n"/>
+      <c r="U119" s="3">
+        <f>IF(A119="","",IF(T119=0,"Set a cap",IF(S119&gt;T119,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4313,8 +5043,14 @@
       </c>
       <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
-      <c r="R120" s="3">
-        <f>IF(A120="","",IF(Q120=0,"Set a cap",IF(P120&gt;Q120,"Over cap - shrink batch","OK")))</f>
+      <c r="R120" s="4" t="n"/>
+      <c r="S120" s="5">
+        <f>IF(A120="","",P120+Q120+R120)</f>
+        <v/>
+      </c>
+      <c r="T120" s="4" t="n"/>
+      <c r="U120" s="3">
+        <f>IF(A120="","",IF(T120=0,"Set a cap",IF(S120&gt;T120,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4344,8 +5080,14 @@
       </c>
       <c r="P121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
-      <c r="R121" s="3">
-        <f>IF(A121="","",IF(Q121=0,"Set a cap",IF(P121&gt;Q121,"Over cap - shrink batch","OK")))</f>
+      <c r="R121" s="4" t="n"/>
+      <c r="S121" s="5">
+        <f>IF(A121="","",P121+Q121+R121)</f>
+        <v/>
+      </c>
+      <c r="T121" s="4" t="n"/>
+      <c r="U121" s="3">
+        <f>IF(A121="","",IF(T121=0,"Set a cap",IF(S121&gt;T121,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4375,8 +5117,14 @@
       </c>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
-      <c r="R122" s="3">
-        <f>IF(A122="","",IF(Q122=0,"Set a cap",IF(P122&gt;Q122,"Over cap - shrink batch","OK")))</f>
+      <c r="R122" s="4" t="n"/>
+      <c r="S122" s="5">
+        <f>IF(A122="","",P122+Q122+R122)</f>
+        <v/>
+      </c>
+      <c r="T122" s="4" t="n"/>
+      <c r="U122" s="3">
+        <f>IF(A122="","",IF(T122=0,"Set a cap",IF(S122&gt;T122,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4406,8 +5154,14 @@
       </c>
       <c r="P123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
-      <c r="R123" s="3">
-        <f>IF(A123="","",IF(Q123=0,"Set a cap",IF(P123&gt;Q123,"Over cap - shrink batch","OK")))</f>
+      <c r="R123" s="4" t="n"/>
+      <c r="S123" s="5">
+        <f>IF(A123="","",P123+Q123+R123)</f>
+        <v/>
+      </c>
+      <c r="T123" s="4" t="n"/>
+      <c r="U123" s="3">
+        <f>IF(A123="","",IF(T123=0,"Set a cap",IF(S123&gt;T123,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4437,8 +5191,14 @@
       </c>
       <c r="P124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
-      <c r="R124" s="3">
-        <f>IF(A124="","",IF(Q124=0,"Set a cap",IF(P124&gt;Q124,"Over cap - shrink batch","OK")))</f>
+      <c r="R124" s="4" t="n"/>
+      <c r="S124" s="5">
+        <f>IF(A124="","",P124+Q124+R124)</f>
+        <v/>
+      </c>
+      <c r="T124" s="4" t="n"/>
+      <c r="U124" s="3">
+        <f>IF(A124="","",IF(T124=0,"Set a cap",IF(S124&gt;T124,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4468,8 +5228,14 @@
       </c>
       <c r="P125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
-      <c r="R125" s="3">
-        <f>IF(A125="","",IF(Q125=0,"Set a cap",IF(P125&gt;Q125,"Over cap - shrink batch","OK")))</f>
+      <c r="R125" s="4" t="n"/>
+      <c r="S125" s="5">
+        <f>IF(A125="","",P125+Q125+R125)</f>
+        <v/>
+      </c>
+      <c r="T125" s="4" t="n"/>
+      <c r="U125" s="3">
+        <f>IF(A125="","",IF(T125=0,"Set a cap",IF(S125&gt;T125,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4499,8 +5265,14 @@
       </c>
       <c r="P126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
-      <c r="R126" s="3">
-        <f>IF(A126="","",IF(Q126=0,"Set a cap",IF(P126&gt;Q126,"Over cap - shrink batch","OK")))</f>
+      <c r="R126" s="4" t="n"/>
+      <c r="S126" s="5">
+        <f>IF(A126="","",P126+Q126+R126)</f>
+        <v/>
+      </c>
+      <c r="T126" s="4" t="n"/>
+      <c r="U126" s="3">
+        <f>IF(A126="","",IF(T126=0,"Set a cap",IF(S126&gt;T126,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4530,8 +5302,14 @@
       </c>
       <c r="P127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
-      <c r="R127" s="3">
-        <f>IF(A127="","",IF(Q127=0,"Set a cap",IF(P127&gt;Q127,"Over cap - shrink batch","OK")))</f>
+      <c r="R127" s="4" t="n"/>
+      <c r="S127" s="5">
+        <f>IF(A127="","",P127+Q127+R127)</f>
+        <v/>
+      </c>
+      <c r="T127" s="4" t="n"/>
+      <c r="U127" s="3">
+        <f>IF(A127="","",IF(T127=0,"Set a cap",IF(S127&gt;T127,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4561,8 +5339,14 @@
       </c>
       <c r="P128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
-      <c r="R128" s="3">
-        <f>IF(A128="","",IF(Q128=0,"Set a cap",IF(P128&gt;Q128,"Over cap - shrink batch","OK")))</f>
+      <c r="R128" s="4" t="n"/>
+      <c r="S128" s="5">
+        <f>IF(A128="","",P128+Q128+R128)</f>
+        <v/>
+      </c>
+      <c r="T128" s="4" t="n"/>
+      <c r="U128" s="3">
+        <f>IF(A128="","",IF(T128=0,"Set a cap",IF(S128&gt;T128,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4592,8 +5376,14 @@
       </c>
       <c r="P129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
-      <c r="R129" s="3">
-        <f>IF(A129="","",IF(Q129=0,"Set a cap",IF(P129&gt;Q129,"Over cap - shrink batch","OK")))</f>
+      <c r="R129" s="4" t="n"/>
+      <c r="S129" s="5">
+        <f>IF(A129="","",P129+Q129+R129)</f>
+        <v/>
+      </c>
+      <c r="T129" s="4" t="n"/>
+      <c r="U129" s="3">
+        <f>IF(A129="","",IF(T129=0,"Set a cap",IF(S129&gt;T129,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4623,8 +5413,14 @@
       </c>
       <c r="P130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
-      <c r="R130" s="3">
-        <f>IF(A130="","",IF(Q130=0,"Set a cap",IF(P130&gt;Q130,"Over cap - shrink batch","OK")))</f>
+      <c r="R130" s="4" t="n"/>
+      <c r="S130" s="5">
+        <f>IF(A130="","",P130+Q130+R130)</f>
+        <v/>
+      </c>
+      <c r="T130" s="4" t="n"/>
+      <c r="U130" s="3">
+        <f>IF(A130="","",IF(T130=0,"Set a cap",IF(S130&gt;T130,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4654,8 +5450,14 @@
       </c>
       <c r="P131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
-      <c r="R131" s="3">
-        <f>IF(A131="","",IF(Q131=0,"Set a cap",IF(P131&gt;Q131,"Over cap - shrink batch","OK")))</f>
+      <c r="R131" s="4" t="n"/>
+      <c r="S131" s="5">
+        <f>IF(A131="","",P131+Q131+R131)</f>
+        <v/>
+      </c>
+      <c r="T131" s="4" t="n"/>
+      <c r="U131" s="3">
+        <f>IF(A131="","",IF(T131=0,"Set a cap",IF(S131&gt;T131,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4685,8 +5487,14 @@
       </c>
       <c r="P132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
-      <c r="R132" s="3">
-        <f>IF(A132="","",IF(Q132=0,"Set a cap",IF(P132&gt;Q132,"Over cap - shrink batch","OK")))</f>
+      <c r="R132" s="4" t="n"/>
+      <c r="S132" s="5">
+        <f>IF(A132="","",P132+Q132+R132)</f>
+        <v/>
+      </c>
+      <c r="T132" s="4" t="n"/>
+      <c r="U132" s="3">
+        <f>IF(A132="","",IF(T132=0,"Set a cap",IF(S132&gt;T132,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4716,8 +5524,14 @@
       </c>
       <c r="P133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
-      <c r="R133" s="3">
-        <f>IF(A133="","",IF(Q133=0,"Set a cap",IF(P133&gt;Q133,"Over cap - shrink batch","OK")))</f>
+      <c r="R133" s="4" t="n"/>
+      <c r="S133" s="5">
+        <f>IF(A133="","",P133+Q133+R133)</f>
+        <v/>
+      </c>
+      <c r="T133" s="4" t="n"/>
+      <c r="U133" s="3">
+        <f>IF(A133="","",IF(T133=0,"Set a cap",IF(S133&gt;T133,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4747,8 +5561,14 @@
       </c>
       <c r="P134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
-      <c r="R134" s="3">
-        <f>IF(A134="","",IF(Q134=0,"Set a cap",IF(P134&gt;Q134,"Over cap - shrink batch","OK")))</f>
+      <c r="R134" s="4" t="n"/>
+      <c r="S134" s="5">
+        <f>IF(A134="","",P134+Q134+R134)</f>
+        <v/>
+      </c>
+      <c r="T134" s="4" t="n"/>
+      <c r="U134" s="3">
+        <f>IF(A134="","",IF(T134=0,"Set a cap",IF(S134&gt;T134,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4778,8 +5598,14 @@
       </c>
       <c r="P135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
-      <c r="R135" s="3">
-        <f>IF(A135="","",IF(Q135=0,"Set a cap",IF(P135&gt;Q135,"Over cap - shrink batch","OK")))</f>
+      <c r="R135" s="4" t="n"/>
+      <c r="S135" s="5">
+        <f>IF(A135="","",P135+Q135+R135)</f>
+        <v/>
+      </c>
+      <c r="T135" s="4" t="n"/>
+      <c r="U135" s="3">
+        <f>IF(A135="","",IF(T135=0,"Set a cap",IF(S135&gt;T135,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4809,8 +5635,14 @@
       </c>
       <c r="P136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
-      <c r="R136" s="3">
-        <f>IF(A136="","",IF(Q136=0,"Set a cap",IF(P136&gt;Q136,"Over cap - shrink batch","OK")))</f>
+      <c r="R136" s="4" t="n"/>
+      <c r="S136" s="5">
+        <f>IF(A136="","",P136+Q136+R136)</f>
+        <v/>
+      </c>
+      <c r="T136" s="4" t="n"/>
+      <c r="U136" s="3">
+        <f>IF(A136="","",IF(T136=0,"Set a cap",IF(S136&gt;T136,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4840,8 +5672,14 @@
       </c>
       <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
-      <c r="R137" s="3">
-        <f>IF(A137="","",IF(Q137=0,"Set a cap",IF(P137&gt;Q137,"Over cap - shrink batch","OK")))</f>
+      <c r="R137" s="4" t="n"/>
+      <c r="S137" s="5">
+        <f>IF(A137="","",P137+Q137+R137)</f>
+        <v/>
+      </c>
+      <c r="T137" s="4" t="n"/>
+      <c r="U137" s="3">
+        <f>IF(A137="","",IF(T137=0,"Set a cap",IF(S137&gt;T137,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4871,8 +5709,14 @@
       </c>
       <c r="P138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
-      <c r="R138" s="3">
-        <f>IF(A138="","",IF(Q138=0,"Set a cap",IF(P138&gt;Q138,"Over cap - shrink batch","OK")))</f>
+      <c r="R138" s="4" t="n"/>
+      <c r="S138" s="5">
+        <f>IF(A138="","",P138+Q138+R138)</f>
+        <v/>
+      </c>
+      <c r="T138" s="4" t="n"/>
+      <c r="U138" s="3">
+        <f>IF(A138="","",IF(T138=0,"Set a cap",IF(S138&gt;T138,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4902,8 +5746,14 @@
       </c>
       <c r="P139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
-      <c r="R139" s="3">
-        <f>IF(A139="","",IF(Q139=0,"Set a cap",IF(P139&gt;Q139,"Over cap - shrink batch","OK")))</f>
+      <c r="R139" s="4" t="n"/>
+      <c r="S139" s="5">
+        <f>IF(A139="","",P139+Q139+R139)</f>
+        <v/>
+      </c>
+      <c r="T139" s="4" t="n"/>
+      <c r="U139" s="3">
+        <f>IF(A139="","",IF(T139=0,"Set a cap",IF(S139&gt;T139,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4933,8 +5783,14 @@
       </c>
       <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
-      <c r="R140" s="3">
-        <f>IF(A140="","",IF(Q140=0,"Set a cap",IF(P140&gt;Q140,"Over cap - shrink batch","OK")))</f>
+      <c r="R140" s="4" t="n"/>
+      <c r="S140" s="5">
+        <f>IF(A140="","",P140+Q140+R140)</f>
+        <v/>
+      </c>
+      <c r="T140" s="4" t="n"/>
+      <c r="U140" s="3">
+        <f>IF(A140="","",IF(T140=0,"Set a cap",IF(S140&gt;T140,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4964,8 +5820,14 @@
       </c>
       <c r="P141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
-      <c r="R141" s="3">
-        <f>IF(A141="","",IF(Q141=0,"Set a cap",IF(P141&gt;Q141,"Over cap - shrink batch","OK")))</f>
+      <c r="R141" s="4" t="n"/>
+      <c r="S141" s="5">
+        <f>IF(A141="","",P141+Q141+R141)</f>
+        <v/>
+      </c>
+      <c r="T141" s="4" t="n"/>
+      <c r="U141" s="3">
+        <f>IF(A141="","",IF(T141=0,"Set a cap",IF(S141&gt;T141,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4995,8 +5857,14 @@
       </c>
       <c r="P142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
-      <c r="R142" s="3">
-        <f>IF(A142="","",IF(Q142=0,"Set a cap",IF(P142&gt;Q142,"Over cap - shrink batch","OK")))</f>
+      <c r="R142" s="4" t="n"/>
+      <c r="S142" s="5">
+        <f>IF(A142="","",P142+Q142+R142)</f>
+        <v/>
+      </c>
+      <c r="T142" s="4" t="n"/>
+      <c r="U142" s="3">
+        <f>IF(A142="","",IF(T142=0,"Set a cap",IF(S142&gt;T142,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5026,8 +5894,14 @@
       </c>
       <c r="P143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
-      <c r="R143" s="3">
-        <f>IF(A143="","",IF(Q143=0,"Set a cap",IF(P143&gt;Q143,"Over cap - shrink batch","OK")))</f>
+      <c r="R143" s="4" t="n"/>
+      <c r="S143" s="5">
+        <f>IF(A143="","",P143+Q143+R143)</f>
+        <v/>
+      </c>
+      <c r="T143" s="4" t="n"/>
+      <c r="U143" s="3">
+        <f>IF(A143="","",IF(T143=0,"Set a cap",IF(S143&gt;T143,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5057,8 +5931,14 @@
       </c>
       <c r="P144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
-      <c r="R144" s="3">
-        <f>IF(A144="","",IF(Q144=0,"Set a cap",IF(P144&gt;Q144,"Over cap - shrink batch","OK")))</f>
+      <c r="R144" s="4" t="n"/>
+      <c r="S144" s="5">
+        <f>IF(A144="","",P144+Q144+R144)</f>
+        <v/>
+      </c>
+      <c r="T144" s="4" t="n"/>
+      <c r="U144" s="3">
+        <f>IF(A144="","",IF(T144=0,"Set a cap",IF(S144&gt;T144,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5088,8 +5968,14 @@
       </c>
       <c r="P145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
-      <c r="R145" s="3">
-        <f>IF(A145="","",IF(Q145=0,"Set a cap",IF(P145&gt;Q145,"Over cap - shrink batch","OK")))</f>
+      <c r="R145" s="4" t="n"/>
+      <c r="S145" s="5">
+        <f>IF(A145="","",P145+Q145+R145)</f>
+        <v/>
+      </c>
+      <c r="T145" s="4" t="n"/>
+      <c r="U145" s="3">
+        <f>IF(A145="","",IF(T145=0,"Set a cap",IF(S145&gt;T145,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5119,8 +6005,14 @@
       </c>
       <c r="P146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
-      <c r="R146" s="3">
-        <f>IF(A146="","",IF(Q146=0,"Set a cap",IF(P146&gt;Q146,"Over cap - shrink batch","OK")))</f>
+      <c r="R146" s="4" t="n"/>
+      <c r="S146" s="5">
+        <f>IF(A146="","",P146+Q146+R146)</f>
+        <v/>
+      </c>
+      <c r="T146" s="4" t="n"/>
+      <c r="U146" s="3">
+        <f>IF(A146="","",IF(T146=0,"Set a cap",IF(S146&gt;T146,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5150,8 +6042,14 @@
       </c>
       <c r="P147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
-      <c r="R147" s="3">
-        <f>IF(A147="","",IF(Q147=0,"Set a cap",IF(P147&gt;Q147,"Over cap - shrink batch","OK")))</f>
+      <c r="R147" s="4" t="n"/>
+      <c r="S147" s="5">
+        <f>IF(A147="","",P147+Q147+R147)</f>
+        <v/>
+      </c>
+      <c r="T147" s="4" t="n"/>
+      <c r="U147" s="3">
+        <f>IF(A147="","",IF(T147=0,"Set a cap",IF(S147&gt;T147,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5181,8 +6079,14 @@
       </c>
       <c r="P148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
-      <c r="R148" s="3">
-        <f>IF(A148="","",IF(Q148=0,"Set a cap",IF(P148&gt;Q148,"Over cap - shrink batch","OK")))</f>
+      <c r="R148" s="4" t="n"/>
+      <c r="S148" s="5">
+        <f>IF(A148="","",P148+Q148+R148)</f>
+        <v/>
+      </c>
+      <c r="T148" s="4" t="n"/>
+      <c r="U148" s="3">
+        <f>IF(A148="","",IF(T148=0,"Set a cap",IF(S148&gt;T148,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5212,8 +6116,14 @@
       </c>
       <c r="P149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
-      <c r="R149" s="3">
-        <f>IF(A149="","",IF(Q149=0,"Set a cap",IF(P149&gt;Q149,"Over cap - shrink batch","OK")))</f>
+      <c r="R149" s="4" t="n"/>
+      <c r="S149" s="5">
+        <f>IF(A149="","",P149+Q149+R149)</f>
+        <v/>
+      </c>
+      <c r="T149" s="4" t="n"/>
+      <c r="U149" s="3">
+        <f>IF(A149="","",IF(T149=0,"Set a cap",IF(S149&gt;T149,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5243,8 +6153,14 @@
       </c>
       <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
-      <c r="R150" s="3">
-        <f>IF(A150="","",IF(Q150=0,"Set a cap",IF(P150&gt;Q150,"Over cap - shrink batch","OK")))</f>
+      <c r="R150" s="4" t="n"/>
+      <c r="S150" s="5">
+        <f>IF(A150="","",P150+Q150+R150)</f>
+        <v/>
+      </c>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="3">
+        <f>IF(A150="","",IF(T150=0,"Set a cap",IF(S150&gt;T150,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5274,8 +6190,14 @@
       </c>
       <c r="P151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
-      <c r="R151" s="3">
-        <f>IF(A151="","",IF(Q151=0,"Set a cap",IF(P151&gt;Q151,"Over cap - shrink batch","OK")))</f>
+      <c r="R151" s="4" t="n"/>
+      <c r="S151" s="5">
+        <f>IF(A151="","",P151+Q151+R151)</f>
+        <v/>
+      </c>
+      <c r="T151" s="4" t="n"/>
+      <c r="U151" s="3">
+        <f>IF(A151="","",IF(T151=0,"Set a cap",IF(S151&gt;T151,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5305,8 +6227,14 @@
       </c>
       <c r="P152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
-      <c r="R152" s="3">
-        <f>IF(A152="","",IF(Q152=0,"Set a cap",IF(P152&gt;Q152,"Over cap - shrink batch","OK")))</f>
+      <c r="R152" s="4" t="n"/>
+      <c r="S152" s="5">
+        <f>IF(A152="","",P152+Q152+R152)</f>
+        <v/>
+      </c>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="3">
+        <f>IF(A152="","",IF(T152=0,"Set a cap",IF(S152&gt;T152,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5336,8 +6264,14 @@
       </c>
       <c r="P153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
-      <c r="R153" s="3">
-        <f>IF(A153="","",IF(Q153=0,"Set a cap",IF(P153&gt;Q153,"Over cap - shrink batch","OK")))</f>
+      <c r="R153" s="4" t="n"/>
+      <c r="S153" s="5">
+        <f>IF(A153="","",P153+Q153+R153)</f>
+        <v/>
+      </c>
+      <c r="T153" s="4" t="n"/>
+      <c r="U153" s="3">
+        <f>IF(A153="","",IF(T153=0,"Set a cap",IF(S153&gt;T153,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5367,8 +6301,14 @@
       </c>
       <c r="P154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
-      <c r="R154" s="3">
-        <f>IF(A154="","",IF(Q154=0,"Set a cap",IF(P154&gt;Q154,"Over cap - shrink batch","OK")))</f>
+      <c r="R154" s="4" t="n"/>
+      <c r="S154" s="5">
+        <f>IF(A154="","",P154+Q154+R154)</f>
+        <v/>
+      </c>
+      <c r="T154" s="4" t="n"/>
+      <c r="U154" s="3">
+        <f>IF(A154="","",IF(T154=0,"Set a cap",IF(S154&gt;T154,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5398,8 +6338,14 @@
       </c>
       <c r="P155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
-      <c r="R155" s="3">
-        <f>IF(A155="","",IF(Q155=0,"Set a cap",IF(P155&gt;Q155,"Over cap - shrink batch","OK")))</f>
+      <c r="R155" s="4" t="n"/>
+      <c r="S155" s="5">
+        <f>IF(A155="","",P155+Q155+R155)</f>
+        <v/>
+      </c>
+      <c r="T155" s="4" t="n"/>
+      <c r="U155" s="3">
+        <f>IF(A155="","",IF(T155=0,"Set a cap",IF(S155&gt;T155,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5429,8 +6375,14 @@
       </c>
       <c r="P156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
-      <c r="R156" s="3">
-        <f>IF(A156="","",IF(Q156=0,"Set a cap",IF(P156&gt;Q156,"Over cap - shrink batch","OK")))</f>
+      <c r="R156" s="4" t="n"/>
+      <c r="S156" s="5">
+        <f>IF(A156="","",P156+Q156+R156)</f>
+        <v/>
+      </c>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="3">
+        <f>IF(A156="","",IF(T156=0,"Set a cap",IF(S156&gt;T156,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5460,8 +6412,14 @@
       </c>
       <c r="P157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
-      <c r="R157" s="3">
-        <f>IF(A157="","",IF(Q157=0,"Set a cap",IF(P157&gt;Q157,"Over cap - shrink batch","OK")))</f>
+      <c r="R157" s="4" t="n"/>
+      <c r="S157" s="5">
+        <f>IF(A157="","",P157+Q157+R157)</f>
+        <v/>
+      </c>
+      <c r="T157" s="4" t="n"/>
+      <c r="U157" s="3">
+        <f>IF(A157="","",IF(T157=0,"Set a cap",IF(S157&gt;T157,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5491,8 +6449,14 @@
       </c>
       <c r="P158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
-      <c r="R158" s="3">
-        <f>IF(A158="","",IF(Q158=0,"Set a cap",IF(P158&gt;Q158,"Over cap - shrink batch","OK")))</f>
+      <c r="R158" s="4" t="n"/>
+      <c r="S158" s="5">
+        <f>IF(A158="","",P158+Q158+R158)</f>
+        <v/>
+      </c>
+      <c r="T158" s="4" t="n"/>
+      <c r="U158" s="3">
+        <f>IF(A158="","",IF(T158=0,"Set a cap",IF(S158&gt;T158,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5522,8 +6486,14 @@
       </c>
       <c r="P159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
-      <c r="R159" s="3">
-        <f>IF(A159="","",IF(Q159=0,"Set a cap",IF(P159&gt;Q159,"Over cap - shrink batch","OK")))</f>
+      <c r="R159" s="4" t="n"/>
+      <c r="S159" s="5">
+        <f>IF(A159="","",P159+Q159+R159)</f>
+        <v/>
+      </c>
+      <c r="T159" s="4" t="n"/>
+      <c r="U159" s="3">
+        <f>IF(A159="","",IF(T159=0,"Set a cap",IF(S159&gt;T159,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5553,8 +6523,14 @@
       </c>
       <c r="P160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
-      <c r="R160" s="3">
-        <f>IF(A160="","",IF(Q160=0,"Set a cap",IF(P160&gt;Q160,"Over cap - shrink batch","OK")))</f>
+      <c r="R160" s="4" t="n"/>
+      <c r="S160" s="5">
+        <f>IF(A160="","",P160+Q160+R160)</f>
+        <v/>
+      </c>
+      <c r="T160" s="4" t="n"/>
+      <c r="U160" s="3">
+        <f>IF(A160="","",IF(T160=0,"Set a cap",IF(S160&gt;T160,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5584,8 +6560,14 @@
       </c>
       <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
-      <c r="R161" s="3">
-        <f>IF(A161="","",IF(Q161=0,"Set a cap",IF(P161&gt;Q161,"Over cap - shrink batch","OK")))</f>
+      <c r="R161" s="4" t="n"/>
+      <c r="S161" s="5">
+        <f>IF(A161="","",P161+Q161+R161)</f>
+        <v/>
+      </c>
+      <c r="T161" s="4" t="n"/>
+      <c r="U161" s="3">
+        <f>IF(A161="","",IF(T161=0,"Set a cap",IF(S161&gt;T161,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5615,8 +6597,14 @@
       </c>
       <c r="P162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
-      <c r="R162" s="3">
-        <f>IF(A162="","",IF(Q162=0,"Set a cap",IF(P162&gt;Q162,"Over cap - shrink batch","OK")))</f>
+      <c r="R162" s="4" t="n"/>
+      <c r="S162" s="5">
+        <f>IF(A162="","",P162+Q162+R162)</f>
+        <v/>
+      </c>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="3">
+        <f>IF(A162="","",IF(T162=0,"Set a cap",IF(S162&gt;T162,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5646,8 +6634,14 @@
       </c>
       <c r="P163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
-      <c r="R163" s="3">
-        <f>IF(A163="","",IF(Q163=0,"Set a cap",IF(P163&gt;Q163,"Over cap - shrink batch","OK")))</f>
+      <c r="R163" s="4" t="n"/>
+      <c r="S163" s="5">
+        <f>IF(A163="","",P163+Q163+R163)</f>
+        <v/>
+      </c>
+      <c r="T163" s="4" t="n"/>
+      <c r="U163" s="3">
+        <f>IF(A163="","",IF(T163=0,"Set a cap",IF(S163&gt;T163,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5677,8 +6671,14 @@
       </c>
       <c r="P164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
-      <c r="R164" s="3">
-        <f>IF(A164="","",IF(Q164=0,"Set a cap",IF(P164&gt;Q164,"Over cap - shrink batch","OK")))</f>
+      <c r="R164" s="4" t="n"/>
+      <c r="S164" s="5">
+        <f>IF(A164="","",P164+Q164+R164)</f>
+        <v/>
+      </c>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="3">
+        <f>IF(A164="","",IF(T164=0,"Set a cap",IF(S164&gt;T164,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5708,8 +6708,14 @@
       </c>
       <c r="P165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
-      <c r="R165" s="3">
-        <f>IF(A165="","",IF(Q165=0,"Set a cap",IF(P165&gt;Q165,"Over cap - shrink batch","OK")))</f>
+      <c r="R165" s="4" t="n"/>
+      <c r="S165" s="5">
+        <f>IF(A165="","",P165+Q165+R165)</f>
+        <v/>
+      </c>
+      <c r="T165" s="4" t="n"/>
+      <c r="U165" s="3">
+        <f>IF(A165="","",IF(T165=0,"Set a cap",IF(S165&gt;T165,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5739,8 +6745,14 @@
       </c>
       <c r="P166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
-      <c r="R166" s="3">
-        <f>IF(A166="","",IF(Q166=0,"Set a cap",IF(P166&gt;Q166,"Over cap - shrink batch","OK")))</f>
+      <c r="R166" s="4" t="n"/>
+      <c r="S166" s="5">
+        <f>IF(A166="","",P166+Q166+R166)</f>
+        <v/>
+      </c>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="3">
+        <f>IF(A166="","",IF(T166=0,"Set a cap",IF(S166&gt;T166,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5770,8 +6782,14 @@
       </c>
       <c r="P167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
-      <c r="R167" s="3">
-        <f>IF(A167="","",IF(Q167=0,"Set a cap",IF(P167&gt;Q167,"Over cap - shrink batch","OK")))</f>
+      <c r="R167" s="4" t="n"/>
+      <c r="S167" s="5">
+        <f>IF(A167="","",P167+Q167+R167)</f>
+        <v/>
+      </c>
+      <c r="T167" s="4" t="n"/>
+      <c r="U167" s="3">
+        <f>IF(A167="","",IF(T167=0,"Set a cap",IF(S167&gt;T167,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5801,8 +6819,14 @@
       </c>
       <c r="P168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
-      <c r="R168" s="3">
-        <f>IF(A168="","",IF(Q168=0,"Set a cap",IF(P168&gt;Q168,"Over cap - shrink batch","OK")))</f>
+      <c r="R168" s="4" t="n"/>
+      <c r="S168" s="5">
+        <f>IF(A168="","",P168+Q168+R168)</f>
+        <v/>
+      </c>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="3">
+        <f>IF(A168="","",IF(T168=0,"Set a cap",IF(S168&gt;T168,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5832,8 +6856,14 @@
       </c>
       <c r="P169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
-      <c r="R169" s="3">
-        <f>IF(A169="","",IF(Q169=0,"Set a cap",IF(P169&gt;Q169,"Over cap - shrink batch","OK")))</f>
+      <c r="R169" s="4" t="n"/>
+      <c r="S169" s="5">
+        <f>IF(A169="","",P169+Q169+R169)</f>
+        <v/>
+      </c>
+      <c r="T169" s="4" t="n"/>
+      <c r="U169" s="3">
+        <f>IF(A169="","",IF(T169=0,"Set a cap",IF(S169&gt;T169,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5863,8 +6893,14 @@
       </c>
       <c r="P170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
-      <c r="R170" s="3">
-        <f>IF(A170="","",IF(Q170=0,"Set a cap",IF(P170&gt;Q170,"Over cap - shrink batch","OK")))</f>
+      <c r="R170" s="4" t="n"/>
+      <c r="S170" s="5">
+        <f>IF(A170="","",P170+Q170+R170)</f>
+        <v/>
+      </c>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="3">
+        <f>IF(A170="","",IF(T170=0,"Set a cap",IF(S170&gt;T170,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5894,8 +6930,14 @@
       </c>
       <c r="P171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
-      <c r="R171" s="3">
-        <f>IF(A171="","",IF(Q171=0,"Set a cap",IF(P171&gt;Q171,"Over cap - shrink batch","OK")))</f>
+      <c r="R171" s="4" t="n"/>
+      <c r="S171" s="5">
+        <f>IF(A171="","",P171+Q171+R171)</f>
+        <v/>
+      </c>
+      <c r="T171" s="4" t="n"/>
+      <c r="U171" s="3">
+        <f>IF(A171="","",IF(T171=0,"Set a cap",IF(S171&gt;T171,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5925,8 +6967,14 @@
       </c>
       <c r="P172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
-      <c r="R172" s="3">
-        <f>IF(A172="","",IF(Q172=0,"Set a cap",IF(P172&gt;Q172,"Over cap - shrink batch","OK")))</f>
+      <c r="R172" s="4" t="n"/>
+      <c r="S172" s="5">
+        <f>IF(A172="","",P172+Q172+R172)</f>
+        <v/>
+      </c>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="3">
+        <f>IF(A172="","",IF(T172=0,"Set a cap",IF(S172&gt;T172,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5956,8 +7004,14 @@
       </c>
       <c r="P173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
-      <c r="R173" s="3">
-        <f>IF(A173="","",IF(Q173=0,"Set a cap",IF(P173&gt;Q173,"Over cap - shrink batch","OK")))</f>
+      <c r="R173" s="4" t="n"/>
+      <c r="S173" s="5">
+        <f>IF(A173="","",P173+Q173+R173)</f>
+        <v/>
+      </c>
+      <c r="T173" s="4" t="n"/>
+      <c r="U173" s="3">
+        <f>IF(A173="","",IF(T173=0,"Set a cap",IF(S173&gt;T173,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -5987,8 +7041,14 @@
       </c>
       <c r="P174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
-      <c r="R174" s="3">
-        <f>IF(A174="","",IF(Q174=0,"Set a cap",IF(P174&gt;Q174,"Over cap - shrink batch","OK")))</f>
+      <c r="R174" s="4" t="n"/>
+      <c r="S174" s="5">
+        <f>IF(A174="","",P174+Q174+R174)</f>
+        <v/>
+      </c>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="3">
+        <f>IF(A174="","",IF(T174=0,"Set a cap",IF(S174&gt;T174,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6018,8 +7078,14 @@
       </c>
       <c r="P175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
-      <c r="R175" s="3">
-        <f>IF(A175="","",IF(Q175=0,"Set a cap",IF(P175&gt;Q175,"Over cap - shrink batch","OK")))</f>
+      <c r="R175" s="4" t="n"/>
+      <c r="S175" s="5">
+        <f>IF(A175="","",P175+Q175+R175)</f>
+        <v/>
+      </c>
+      <c r="T175" s="4" t="n"/>
+      <c r="U175" s="3">
+        <f>IF(A175="","",IF(T175=0,"Set a cap",IF(S175&gt;T175,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6049,8 +7115,14 @@
       </c>
       <c r="P176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
-      <c r="R176" s="3">
-        <f>IF(A176="","",IF(Q176=0,"Set a cap",IF(P176&gt;Q176,"Over cap - shrink batch","OK")))</f>
+      <c r="R176" s="4" t="n"/>
+      <c r="S176" s="5">
+        <f>IF(A176="","",P176+Q176+R176)</f>
+        <v/>
+      </c>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="3">
+        <f>IF(A176="","",IF(T176=0,"Set a cap",IF(S176&gt;T176,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6080,8 +7152,14 @@
       </c>
       <c r="P177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
-      <c r="R177" s="3">
-        <f>IF(A177="","",IF(Q177=0,"Set a cap",IF(P177&gt;Q177,"Over cap - shrink batch","OK")))</f>
+      <c r="R177" s="4" t="n"/>
+      <c r="S177" s="5">
+        <f>IF(A177="","",P177+Q177+R177)</f>
+        <v/>
+      </c>
+      <c r="T177" s="4" t="n"/>
+      <c r="U177" s="3">
+        <f>IF(A177="","",IF(T177=0,"Set a cap",IF(S177&gt;T177,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6111,8 +7189,14 @@
       </c>
       <c r="P178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
-      <c r="R178" s="3">
-        <f>IF(A178="","",IF(Q178=0,"Set a cap",IF(P178&gt;Q178,"Over cap - shrink batch","OK")))</f>
+      <c r="R178" s="4" t="n"/>
+      <c r="S178" s="5">
+        <f>IF(A178="","",P178+Q178+R178)</f>
+        <v/>
+      </c>
+      <c r="T178" s="4" t="n"/>
+      <c r="U178" s="3">
+        <f>IF(A178="","",IF(T178=0,"Set a cap",IF(S178&gt;T178,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6142,8 +7226,14 @@
       </c>
       <c r="P179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
-      <c r="R179" s="3">
-        <f>IF(A179="","",IF(Q179=0,"Set a cap",IF(P179&gt;Q179,"Over cap - shrink batch","OK")))</f>
+      <c r="R179" s="4" t="n"/>
+      <c r="S179" s="5">
+        <f>IF(A179="","",P179+Q179+R179)</f>
+        <v/>
+      </c>
+      <c r="T179" s="4" t="n"/>
+      <c r="U179" s="3">
+        <f>IF(A179="","",IF(T179=0,"Set a cap",IF(S179&gt;T179,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6173,8 +7263,14 @@
       </c>
       <c r="P180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
-      <c r="R180" s="3">
-        <f>IF(A180="","",IF(Q180=0,"Set a cap",IF(P180&gt;Q180,"Over cap - shrink batch","OK")))</f>
+      <c r="R180" s="4" t="n"/>
+      <c r="S180" s="5">
+        <f>IF(A180="","",P180+Q180+R180)</f>
+        <v/>
+      </c>
+      <c r="T180" s="4" t="n"/>
+      <c r="U180" s="3">
+        <f>IF(A180="","",IF(T180=0,"Set a cap",IF(S180&gt;T180,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6204,8 +7300,14 @@
       </c>
       <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
-      <c r="R181" s="3">
-        <f>IF(A181="","",IF(Q181=0,"Set a cap",IF(P181&gt;Q181,"Over cap - shrink batch","OK")))</f>
+      <c r="R181" s="4" t="n"/>
+      <c r="S181" s="5">
+        <f>IF(A181="","",P181+Q181+R181)</f>
+        <v/>
+      </c>
+      <c r="T181" s="4" t="n"/>
+      <c r="U181" s="3">
+        <f>IF(A181="","",IF(T181=0,"Set a cap",IF(S181&gt;T181,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6235,8 +7337,14 @@
       </c>
       <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
-      <c r="R182" s="3">
-        <f>IF(A182="","",IF(Q182=0,"Set a cap",IF(P182&gt;Q182,"Over cap - shrink batch","OK")))</f>
+      <c r="R182" s="4" t="n"/>
+      <c r="S182" s="5">
+        <f>IF(A182="","",P182+Q182+R182)</f>
+        <v/>
+      </c>
+      <c r="T182" s="4" t="n"/>
+      <c r="U182" s="3">
+        <f>IF(A182="","",IF(T182=0,"Set a cap",IF(S182&gt;T182,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6266,8 +7374,14 @@
       </c>
       <c r="P183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
-      <c r="R183" s="3">
-        <f>IF(A183="","",IF(Q183=0,"Set a cap",IF(P183&gt;Q183,"Over cap - shrink batch","OK")))</f>
+      <c r="R183" s="4" t="n"/>
+      <c r="S183" s="5">
+        <f>IF(A183="","",P183+Q183+R183)</f>
+        <v/>
+      </c>
+      <c r="T183" s="4" t="n"/>
+      <c r="U183" s="3">
+        <f>IF(A183="","",IF(T183=0,"Set a cap",IF(S183&gt;T183,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6297,8 +7411,14 @@
       </c>
       <c r="P184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
-      <c r="R184" s="3">
-        <f>IF(A184="","",IF(Q184=0,"Set a cap",IF(P184&gt;Q184,"Over cap - shrink batch","OK")))</f>
+      <c r="R184" s="4" t="n"/>
+      <c r="S184" s="5">
+        <f>IF(A184="","",P184+Q184+R184)</f>
+        <v/>
+      </c>
+      <c r="T184" s="4" t="n"/>
+      <c r="U184" s="3">
+        <f>IF(A184="","",IF(T184=0,"Set a cap",IF(S184&gt;T184,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6328,8 +7448,14 @@
       </c>
       <c r="P185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
-      <c r="R185" s="3">
-        <f>IF(A185="","",IF(Q185=0,"Set a cap",IF(P185&gt;Q185,"Over cap - shrink batch","OK")))</f>
+      <c r="R185" s="4" t="n"/>
+      <c r="S185" s="5">
+        <f>IF(A185="","",P185+Q185+R185)</f>
+        <v/>
+      </c>
+      <c r="T185" s="4" t="n"/>
+      <c r="U185" s="3">
+        <f>IF(A185="","",IF(T185=0,"Set a cap",IF(S185&gt;T185,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6359,8 +7485,14 @@
       </c>
       <c r="P186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
-      <c r="R186" s="3">
-        <f>IF(A186="","",IF(Q186=0,"Set a cap",IF(P186&gt;Q186,"Over cap - shrink batch","OK")))</f>
+      <c r="R186" s="4" t="n"/>
+      <c r="S186" s="5">
+        <f>IF(A186="","",P186+Q186+R186)</f>
+        <v/>
+      </c>
+      <c r="T186" s="4" t="n"/>
+      <c r="U186" s="3">
+        <f>IF(A186="","",IF(T186=0,"Set a cap",IF(S186&gt;T186,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6390,8 +7522,14 @@
       </c>
       <c r="P187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
-      <c r="R187" s="3">
-        <f>IF(A187="","",IF(Q187=0,"Set a cap",IF(P187&gt;Q187,"Over cap - shrink batch","OK")))</f>
+      <c r="R187" s="4" t="n"/>
+      <c r="S187" s="5">
+        <f>IF(A187="","",P187+Q187+R187)</f>
+        <v/>
+      </c>
+      <c r="T187" s="4" t="n"/>
+      <c r="U187" s="3">
+        <f>IF(A187="","",IF(T187=0,"Set a cap",IF(S187&gt;T187,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6421,8 +7559,14 @@
       </c>
       <c r="P188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
-      <c r="R188" s="3">
-        <f>IF(A188="","",IF(Q188=0,"Set a cap",IF(P188&gt;Q188,"Over cap - shrink batch","OK")))</f>
+      <c r="R188" s="4" t="n"/>
+      <c r="S188" s="5">
+        <f>IF(A188="","",P188+Q188+R188)</f>
+        <v/>
+      </c>
+      <c r="T188" s="4" t="n"/>
+      <c r="U188" s="3">
+        <f>IF(A188="","",IF(T188=0,"Set a cap",IF(S188&gt;T188,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6452,8 +7596,14 @@
       </c>
       <c r="P189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
-      <c r="R189" s="3">
-        <f>IF(A189="","",IF(Q189=0,"Set a cap",IF(P189&gt;Q189,"Over cap - shrink batch","OK")))</f>
+      <c r="R189" s="4" t="n"/>
+      <c r="S189" s="5">
+        <f>IF(A189="","",P189+Q189+R189)</f>
+        <v/>
+      </c>
+      <c r="T189" s="4" t="n"/>
+      <c r="U189" s="3">
+        <f>IF(A189="","",IF(T189=0,"Set a cap",IF(S189&gt;T189,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6483,8 +7633,14 @@
       </c>
       <c r="P190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
-      <c r="R190" s="3">
-        <f>IF(A190="","",IF(Q190=0,"Set a cap",IF(P190&gt;Q190,"Over cap - shrink batch","OK")))</f>
+      <c r="R190" s="4" t="n"/>
+      <c r="S190" s="5">
+        <f>IF(A190="","",P190+Q190+R190)</f>
+        <v/>
+      </c>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="3">
+        <f>IF(A190="","",IF(T190=0,"Set a cap",IF(S190&gt;T190,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6514,8 +7670,14 @@
       </c>
       <c r="P191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
-      <c r="R191" s="3">
-        <f>IF(A191="","",IF(Q191=0,"Set a cap",IF(P191&gt;Q191,"Over cap - shrink batch","OK")))</f>
+      <c r="R191" s="4" t="n"/>
+      <c r="S191" s="5">
+        <f>IF(A191="","",P191+Q191+R191)</f>
+        <v/>
+      </c>
+      <c r="T191" s="4" t="n"/>
+      <c r="U191" s="3">
+        <f>IF(A191="","",IF(T191=0,"Set a cap",IF(S191&gt;T191,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6545,8 +7707,14 @@
       </c>
       <c r="P192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
-      <c r="R192" s="3">
-        <f>IF(A192="","",IF(Q192=0,"Set a cap",IF(P192&gt;Q192,"Over cap - shrink batch","OK")))</f>
+      <c r="R192" s="4" t="n"/>
+      <c r="S192" s="5">
+        <f>IF(A192="","",P192+Q192+R192)</f>
+        <v/>
+      </c>
+      <c r="T192" s="4" t="n"/>
+      <c r="U192" s="3">
+        <f>IF(A192="","",IF(T192=0,"Set a cap",IF(S192&gt;T192,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6576,8 +7744,14 @@
       </c>
       <c r="P193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
-      <c r="R193" s="3">
-        <f>IF(A193="","",IF(Q193=0,"Set a cap",IF(P193&gt;Q193,"Over cap - shrink batch","OK")))</f>
+      <c r="R193" s="4" t="n"/>
+      <c r="S193" s="5">
+        <f>IF(A193="","",P193+Q193+R193)</f>
+        <v/>
+      </c>
+      <c r="T193" s="4" t="n"/>
+      <c r="U193" s="3">
+        <f>IF(A193="","",IF(T193=0,"Set a cap",IF(S193&gt;T193,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6607,8 +7781,14 @@
       </c>
       <c r="P194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
-      <c r="R194" s="3">
-        <f>IF(A194="","",IF(Q194=0,"Set a cap",IF(P194&gt;Q194,"Over cap - shrink batch","OK")))</f>
+      <c r="R194" s="4" t="n"/>
+      <c r="S194" s="5">
+        <f>IF(A194="","",P194+Q194+R194)</f>
+        <v/>
+      </c>
+      <c r="T194" s="4" t="n"/>
+      <c r="U194" s="3">
+        <f>IF(A194="","",IF(T194=0,"Set a cap",IF(S194&gt;T194,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6638,8 +7818,14 @@
       </c>
       <c r="P195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
-      <c r="R195" s="3">
-        <f>IF(A195="","",IF(Q195=0,"Set a cap",IF(P195&gt;Q195,"Over cap - shrink batch","OK")))</f>
+      <c r="R195" s="4" t="n"/>
+      <c r="S195" s="5">
+        <f>IF(A195="","",P195+Q195+R195)</f>
+        <v/>
+      </c>
+      <c r="T195" s="4" t="n"/>
+      <c r="U195" s="3">
+        <f>IF(A195="","",IF(T195=0,"Set a cap",IF(S195&gt;T195,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6669,8 +7855,14 @@
       </c>
       <c r="P196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
-      <c r="R196" s="3">
-        <f>IF(A196="","",IF(Q196=0,"Set a cap",IF(P196&gt;Q196,"Over cap - shrink batch","OK")))</f>
+      <c r="R196" s="4" t="n"/>
+      <c r="S196" s="5">
+        <f>IF(A196="","",P196+Q196+R196)</f>
+        <v/>
+      </c>
+      <c r="T196" s="4" t="n"/>
+      <c r="U196" s="3">
+        <f>IF(A196="","",IF(T196=0,"Set a cap",IF(S196&gt;T196,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6700,8 +7892,14 @@
       </c>
       <c r="P197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
-      <c r="R197" s="3">
-        <f>IF(A197="","",IF(Q197=0,"Set a cap",IF(P197&gt;Q197,"Over cap - shrink batch","OK")))</f>
+      <c r="R197" s="4" t="n"/>
+      <c r="S197" s="5">
+        <f>IF(A197="","",P197+Q197+R197)</f>
+        <v/>
+      </c>
+      <c r="T197" s="4" t="n"/>
+      <c r="U197" s="3">
+        <f>IF(A197="","",IF(T197=0,"Set a cap",IF(S197&gt;T197,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6731,8 +7929,14 @@
       </c>
       <c r="P198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
-      <c r="R198" s="3">
-        <f>IF(A198="","",IF(Q198=0,"Set a cap",IF(P198&gt;Q198,"Over cap - shrink batch","OK")))</f>
+      <c r="R198" s="4" t="n"/>
+      <c r="S198" s="5">
+        <f>IF(A198="","",P198+Q198+R198)</f>
+        <v/>
+      </c>
+      <c r="T198" s="4" t="n"/>
+      <c r="U198" s="3">
+        <f>IF(A198="","",IF(T198=0,"Set a cap",IF(S198&gt;T198,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6762,8 +7966,14 @@
       </c>
       <c r="P199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
-      <c r="R199" s="3">
-        <f>IF(A199="","",IF(Q199=0,"Set a cap",IF(P199&gt;Q199,"Over cap - shrink batch","OK")))</f>
+      <c r="R199" s="4" t="n"/>
+      <c r="S199" s="5">
+        <f>IF(A199="","",P199+Q199+R199)</f>
+        <v/>
+      </c>
+      <c r="T199" s="4" t="n"/>
+      <c r="U199" s="3">
+        <f>IF(A199="","",IF(T199=0,"Set a cap",IF(S199&gt;T199,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6793,8 +8003,14 @@
       </c>
       <c r="P200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
-      <c r="R200" s="3">
-        <f>IF(A200="","",IF(Q200=0,"Set a cap",IF(P200&gt;Q200,"Over cap - shrink batch","OK")))</f>
+      <c r="R200" s="4" t="n"/>
+      <c r="S200" s="5">
+        <f>IF(A200="","",P200+Q200+R200)</f>
+        <v/>
+      </c>
+      <c r="T200" s="4" t="n"/>
+      <c r="U200" s="3">
+        <f>IF(A200="","",IF(T200=0,"Set a cap",IF(S200&gt;T200,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6824,8 +8040,14 @@
       </c>
       <c r="P201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
-      <c r="R201" s="3">
-        <f>IF(A201="","",IF(Q201=0,"Set a cap",IF(P201&gt;Q201,"Over cap - shrink batch","OK")))</f>
+      <c r="R201" s="4" t="n"/>
+      <c r="S201" s="5">
+        <f>IF(A201="","",P201+Q201+R201)</f>
+        <v/>
+      </c>
+      <c r="T201" s="4" t="n"/>
+      <c r="U201" s="3">
+        <f>IF(A201="","",IF(T201=0,"Set a cap",IF(S201&gt;T201,"Over cap - three batches lock too much cash; shrink the batch","OK")))</f>
         <v/>
       </c>
     </row>
@@ -6837,7 +8059,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="T2:T201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Test,Hold,Drop,Scale"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6867,7 +8089,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Score every candidate on the three axes (pain value, true cost, content amplifiability) and price from value. Value gap decides: prioritize / traffic / drop. One rule shared with Unit Economics: GM ≥60% with positive consumer surplus = Profit product; 50–60% = Traffic product; below 50% = Thin (rework); no margin left = Drop.</t>
+          <t>Score every candidate on the three axes (pain value, true cost, content amplifiability) and price from value. Value gap decides: prioritize / traffic / drop. One rule shared with Unit Economics (the 60% cut-off is an aiOS default; CC gives ≈50–60% = traffic product): GM ≥60% with positive consumer surplus = Profit product; 50–60% = Traffic product; below 50% = Thin (rework); no margin left = Drop. Cash check: CC's 'three batches in motion' (one selling in the destination warehouse, one in transit, one in production) all lock cash at once — the argument against blind stocking.</t>
         </is>
       </c>
     </row>
